--- a/playlists_02_A.xlsx
+++ b/playlists_02_A.xlsx
@@ -19,16 +19,16 @@
     <t>0NGAZxHanS9e0iNHpR8f2W</t>
   </si>
   <si>
-    <t>eletronico 2026</t>
+    <t>eletro</t>
   </si>
   <si>
     <t>33uRcSdNVZijCXq6qQnpuU</t>
   </si>
   <si>
-    <t>vintage culture</t>
+    <t>acraze</t>
   </si>
   <si>
-    <t>28uJnu5EsrGml2tBd7y8ts</t>
+    <t>4pnp4w9g30yLfVIAFnZMRd</t>
   </si>
   <si>
     <t>eletronicas 2026 mais tocadas</t>
@@ -43,28 +43,13 @@
     <t>4cdyqaBREB68H77QKCrKP1</t>
   </si>
   <si>
-    <t>eletro</t>
-  </si>
-  <si>
     <t>6GYMqO7rTioPxDYkyA6pFS</t>
-  </si>
-  <si>
-    <t>illusionize</t>
-  </si>
-  <si>
-    <t>3RloA7E4XMItSP4FjMBv3L</t>
   </si>
   <si>
     <t>eletronica</t>
   </si>
   <si>
     <t>7zQ9BS4fMLYFbybqv6ckFj</t>
-  </si>
-  <si>
-    <t>boris brejcha</t>
-  </si>
-  <si>
-    <t>6caPJFLv1wesmM7gwK1ACy</t>
   </si>
   <si>
     <t>tomorrowland</t>
@@ -85,10 +70,22 @@
     <t>4Yhgfc6VDbmIkHnix1Y903</t>
   </si>
   <si>
-    <t>eletronicas 2026 as melhores</t>
+    <t>4ATN09xTbTcxu84cMKux9O</t>
   </si>
   <si>
-    <t>4ATN09xTbTcxu84cMKux9O</t>
+    <t>eletronico 2026</t>
+  </si>
+  <si>
+    <t>vintage culture</t>
+  </si>
+  <si>
+    <t>28uJnu5EsrGml2tBd7y8ts</t>
+  </si>
+  <si>
+    <t>illusionize</t>
+  </si>
+  <si>
+    <t>3RloA7E4XMItSP4FjMBv3L</t>
   </si>
   <si>
     <t>6gJj32s2qLIYTnAJwjBSrF</t>
@@ -98,6 +95,9 @@
   </si>
   <si>
     <t>ele</t>
+  </si>
+  <si>
+    <t>eletronicas 2026 as melhores</t>
   </si>
 </sst>
 </file>
@@ -154,7 +154,7 @@
   <cellStyleXfs count="1">
     <xf borderId="0" fillId="0" fontId="0" numFmtId="0" applyAlignment="1" applyFont="1"/>
   </cellStyleXfs>
-  <cellXfs count="8">
+  <cellXfs count="9">
     <xf borderId="0" fillId="0" fontId="0" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
       <alignment readingOrder="0" shrinkToFit="0" vertical="bottom" wrapText="0"/>
     </xf>
@@ -168,6 +168,9 @@
       <alignment readingOrder="0"/>
     </xf>
     <xf borderId="0" fillId="2" fontId="2" numFmtId="0" xfId="0" applyFont="1"/>
+    <xf borderId="0" fillId="2" fontId="3" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
+      <alignment readingOrder="0" vertical="bottom"/>
+    </xf>
     <xf borderId="1" fillId="2" fontId="1" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
       <alignment readingOrder="0" vertical="bottom"/>
     </xf>
@@ -415,13 +418,13 @@
       <c r="H1" s="4"/>
     </row>
     <row r="2" ht="36.0" customHeight="1">
-      <c r="D2" s="1" t="s">
-        <v>4</v>
-      </c>
-      <c r="E2" s="1" t="s">
-        <v>5</v>
-      </c>
-      <c r="F2" s="5" t="s">
+      <c r="D2" s="5" t="s">
+        <v>4</v>
+      </c>
+      <c r="E2" s="6" t="s">
+        <v>5</v>
+      </c>
+      <c r="F2" s="6" t="s">
         <v>6</v>
       </c>
       <c r="G2" s="1" t="s">
@@ -436,56 +439,56 @@
       <c r="E3" s="1" t="s">
         <v>9</v>
       </c>
-      <c r="F3" s="5" t="s">
-        <v>10</v>
+      <c r="F3" s="6" t="s">
+        <v>2</v>
       </c>
       <c r="G3" s="1" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="H3" s="4"/>
     </row>
     <row r="4" ht="36.0" customHeight="1">
-      <c r="D4" s="6" t="s">
+      <c r="D4" s="5" t="s">
+        <v>4</v>
+      </c>
+      <c r="E4" s="6" t="s">
+        <v>5</v>
+      </c>
+      <c r="F4" s="1" t="s">
+        <v>11</v>
+      </c>
+      <c r="G4" s="6" t="s">
         <v>12</v>
       </c>
-      <c r="E4" s="1" t="s">
+      <c r="H4" s="4"/>
+    </row>
+    <row r="5" ht="36.0" customHeight="1">
+      <c r="D5" s="5" t="s">
+        <v>4</v>
+      </c>
+      <c r="E5" s="6" t="s">
+        <v>5</v>
+      </c>
+      <c r="F5" s="3" t="s">
         <v>13</v>
       </c>
-      <c r="F4" s="1" t="s">
+      <c r="G5" s="3" t="s">
         <v>14</v>
       </c>
-      <c r="G4" s="5" t="s">
+      <c r="H5" s="4"/>
+    </row>
+    <row r="6" ht="36.0" customHeight="1">
+      <c r="D6" s="7" t="s">
         <v>15</v>
       </c>
-      <c r="H4" s="4"/>
-    </row>
-    <row r="5" ht="36.0" customHeight="1">
-      <c r="D5" s="6" t="s">
+      <c r="E6" s="1" t="s">
         <v>16</v>
       </c>
-      <c r="E5" s="1" t="s">
-        <v>17</v>
-      </c>
-      <c r="F5" s="3" t="s">
+      <c r="F6" s="6" t="s">
+        <v>17</v>
+      </c>
+      <c r="G6" s="1" t="s">
         <v>18</v>
-      </c>
-      <c r="G5" s="3" t="s">
-        <v>19</v>
-      </c>
-      <c r="H5" s="4"/>
-    </row>
-    <row r="6" ht="36.0" customHeight="1">
-      <c r="D6" s="6" t="s">
-        <v>20</v>
-      </c>
-      <c r="E6" s="1" t="s">
-        <v>21</v>
-      </c>
-      <c r="F6" s="5" t="s">
-        <v>22</v>
-      </c>
-      <c r="G6" s="1" t="s">
-        <v>23</v>
       </c>
       <c r="H6" s="4"/>
     </row>
@@ -496,11 +499,11 @@
       <c r="E7" s="1" t="s">
         <v>9</v>
       </c>
-      <c r="F7" s="5" t="s">
-        <v>24</v>
+      <c r="F7" s="6" t="s">
+        <v>17</v>
       </c>
       <c r="G7" s="3" t="s">
-        <v>25</v>
+        <v>19</v>
       </c>
       <c r="H7" s="4"/>
     </row>
@@ -512,7 +515,7 @@
         <v>1</v>
       </c>
       <c r="F8" s="2" t="s">
-        <v>2</v>
+        <v>20</v>
       </c>
       <c r="G8" s="1" t="s">
         <v>7</v>
@@ -521,10 +524,10 @@
     </row>
     <row r="9" ht="36.0" customHeight="1">
       <c r="D9" s="1" t="s">
-        <v>4</v>
+        <v>21</v>
       </c>
       <c r="E9" s="1" t="s">
-        <v>5</v>
+        <v>22</v>
       </c>
       <c r="F9" s="2" t="s">
         <v>2</v>
@@ -535,62 +538,62 @@
       <c r="H9" s="4"/>
     </row>
     <row r="10" ht="36.0" customHeight="1">
-      <c r="D10" s="1" t="s">
-        <v>8</v>
-      </c>
-      <c r="E10" s="1" t="s">
-        <v>9</v>
+      <c r="D10" s="5" t="s">
+        <v>4</v>
+      </c>
+      <c r="E10" s="6" t="s">
+        <v>5</v>
       </c>
       <c r="F10" s="1" t="s">
+        <v>11</v>
+      </c>
+      <c r="G10" s="3" t="s">
         <v>14</v>
       </c>
-      <c r="G10" s="3" t="s">
-        <v>19</v>
-      </c>
       <c r="H10" s="4"/>
     </row>
     <row r="11" ht="36.0" customHeight="1">
-      <c r="D11" s="6" t="s">
+      <c r="D11" s="5" t="s">
+        <v>4</v>
+      </c>
+      <c r="E11" s="6" t="s">
+        <v>5</v>
+      </c>
+      <c r="F11" s="6" t="s">
+        <v>17</v>
+      </c>
+      <c r="G11" s="1" t="s">
+        <v>18</v>
+      </c>
+      <c r="H11" s="4"/>
+    </row>
+    <row r="12" ht="36.0" customHeight="1">
+      <c r="D12" s="5" t="s">
+        <v>4</v>
+      </c>
+      <c r="E12" s="6" t="s">
+        <v>5</v>
+      </c>
+      <c r="F12" s="2" t="s">
+        <v>2</v>
+      </c>
+      <c r="G12" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="H12" s="4"/>
+    </row>
+    <row r="13" ht="36.0" customHeight="1">
+      <c r="D13" s="5" t="s">
+        <v>4</v>
+      </c>
+      <c r="E13" s="6" t="s">
+        <v>5</v>
+      </c>
+      <c r="F13" s="1" t="s">
+        <v>11</v>
+      </c>
+      <c r="G13" s="6" t="s">
         <v>12</v>
-      </c>
-      <c r="E11" s="1" t="s">
-        <v>13</v>
-      </c>
-      <c r="F11" s="5" t="s">
-        <v>22</v>
-      </c>
-      <c r="G11" s="1" t="s">
-        <v>23</v>
-      </c>
-      <c r="H11" s="4"/>
-    </row>
-    <row r="12" ht="36.0" customHeight="1">
-      <c r="D12" s="6" t="s">
-        <v>16</v>
-      </c>
-      <c r="E12" s="1" t="s">
-        <v>17</v>
-      </c>
-      <c r="F12" s="2" t="s">
-        <v>2</v>
-      </c>
-      <c r="G12" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="H12" s="4"/>
-    </row>
-    <row r="13" ht="36.0" customHeight="1">
-      <c r="D13" s="6" t="s">
-        <v>20</v>
-      </c>
-      <c r="E13" s="1" t="s">
-        <v>21</v>
-      </c>
-      <c r="F13" s="1" t="s">
-        <v>14</v>
-      </c>
-      <c r="G13" s="5" t="s">
-        <v>15</v>
       </c>
       <c r="H13" s="4"/>
     </row>
@@ -602,10 +605,10 @@
         <v>9</v>
       </c>
       <c r="F14" s="2" t="s">
-        <v>2</v>
+        <v>20</v>
       </c>
       <c r="G14" s="1" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="H14" s="4"/>
     </row>
@@ -616,8 +619,8 @@
       <c r="E15" s="1" t="s">
         <v>1</v>
       </c>
-      <c r="F15" s="5" t="s">
-        <v>14</v>
+      <c r="F15" s="6" t="s">
+        <v>11</v>
       </c>
       <c r="G15" s="1" t="s">
         <v>7</v>
@@ -625,10 +628,10 @@
       <c r="H15" s="4"/>
     </row>
     <row r="16" ht="36.0" customHeight="1">
-      <c r="D16" s="1" t="s">
-        <v>4</v>
-      </c>
-      <c r="E16" s="1" t="s">
+      <c r="D16" s="5" t="s">
+        <v>4</v>
+      </c>
+      <c r="E16" s="6" t="s">
         <v>5</v>
       </c>
       <c r="F16" s="2" t="s">
@@ -647,55 +650,55 @@
         <v>9</v>
       </c>
       <c r="F17" s="2" t="s">
-        <v>10</v>
+        <v>2</v>
       </c>
       <c r="G17" s="1" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="H17" s="4"/>
     </row>
     <row r="18" ht="36.0" customHeight="1">
-      <c r="D18" s="6" t="s">
+      <c r="D18" s="7" t="s">
+        <v>23</v>
+      </c>
+      <c r="E18" s="1" t="s">
+        <v>24</v>
+      </c>
+      <c r="F18" s="3" t="s">
+        <v>13</v>
+      </c>
+      <c r="G18" s="3" t="s">
+        <v>14</v>
+      </c>
+      <c r="H18" s="4"/>
+    </row>
+    <row r="19" ht="36.0" customHeight="1">
+      <c r="D19" s="5" t="s">
+        <v>4</v>
+      </c>
+      <c r="E19" s="6" t="s">
+        <v>5</v>
+      </c>
+      <c r="F19" s="6" t="s">
+        <v>11</v>
+      </c>
+      <c r="G19" s="1" t="s">
+        <v>10</v>
+      </c>
+      <c r="H19" s="4"/>
+    </row>
+    <row r="20" ht="36.0" customHeight="1">
+      <c r="D20" s="5" t="s">
+        <v>4</v>
+      </c>
+      <c r="E20" s="6" t="s">
+        <v>5</v>
+      </c>
+      <c r="F20" s="1" t="s">
+        <v>11</v>
+      </c>
+      <c r="G20" s="6" t="s">
         <v>12</v>
-      </c>
-      <c r="E18" s="1" t="s">
-        <v>13</v>
-      </c>
-      <c r="F18" s="3" t="s">
-        <v>18</v>
-      </c>
-      <c r="G18" s="3" t="s">
-        <v>19</v>
-      </c>
-      <c r="H18" s="4"/>
-    </row>
-    <row r="19" ht="36.0" customHeight="1">
-      <c r="D19" s="6" t="s">
-        <v>16</v>
-      </c>
-      <c r="E19" s="1" t="s">
-        <v>17</v>
-      </c>
-      <c r="F19" s="5" t="s">
-        <v>14</v>
-      </c>
-      <c r="G19" s="1" t="s">
-        <v>11</v>
-      </c>
-      <c r="H19" s="4"/>
-    </row>
-    <row r="20" ht="36.0" customHeight="1">
-      <c r="D20" s="6" t="s">
-        <v>20</v>
-      </c>
-      <c r="E20" s="1" t="s">
-        <v>21</v>
-      </c>
-      <c r="F20" s="1" t="s">
-        <v>14</v>
-      </c>
-      <c r="G20" s="5" t="s">
-        <v>15</v>
       </c>
       <c r="H20" s="4"/>
     </row>
@@ -706,11 +709,11 @@
       <c r="E21" s="1" t="s">
         <v>9</v>
       </c>
-      <c r="F21" s="5" t="s">
-        <v>24</v>
+      <c r="F21" s="6" t="s">
+        <v>17</v>
       </c>
       <c r="G21" s="3" t="s">
-        <v>25</v>
+        <v>19</v>
       </c>
       <c r="H21" s="4"/>
     </row>
@@ -731,76 +734,76 @@
     </row>
     <row r="23" ht="36.0" customHeight="1">
       <c r="D23" s="1" t="s">
-        <v>4</v>
+        <v>21</v>
       </c>
       <c r="E23" s="1" t="s">
-        <v>5</v>
+        <v>22</v>
       </c>
       <c r="F23" s="2" t="s">
-        <v>2</v>
-      </c>
-      <c r="G23" s="5" t="s">
-        <v>15</v>
+        <v>20</v>
+      </c>
+      <c r="G23" s="6" t="s">
+        <v>12</v>
       </c>
       <c r="H23" s="4"/>
     </row>
     <row r="24" ht="36.0" customHeight="1">
-      <c r="D24" s="1" t="s">
-        <v>8</v>
-      </c>
-      <c r="E24" s="1" t="s">
-        <v>9</v>
-      </c>
-      <c r="F24" s="5" t="s">
-        <v>22</v>
+      <c r="D24" s="5" t="s">
+        <v>4</v>
+      </c>
+      <c r="E24" s="6" t="s">
+        <v>5</v>
+      </c>
+      <c r="F24" s="6" t="s">
+        <v>17</v>
       </c>
       <c r="G24" s="1" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="H24" s="4"/>
     </row>
     <row r="25" ht="36.0" customHeight="1">
-      <c r="D25" s="6" t="s">
-        <v>12</v>
+      <c r="D25" s="7" t="s">
+        <v>23</v>
       </c>
       <c r="E25" s="1" t="s">
-        <v>13</v>
+        <v>24</v>
       </c>
       <c r="F25" s="2" t="s">
-        <v>2</v>
+        <v>20</v>
       </c>
       <c r="G25" s="3" t="s">
+        <v>25</v>
+      </c>
+      <c r="H25" s="3"/>
+    </row>
+    <row r="26" ht="36.0" customHeight="1">
+      <c r="D26" s="5" t="s">
+        <v>4</v>
+      </c>
+      <c r="E26" s="6" t="s">
+        <v>5</v>
+      </c>
+      <c r="F26" s="6" t="s">
+        <v>17</v>
+      </c>
+      <c r="G26" s="1" t="s">
+        <v>18</v>
+      </c>
+      <c r="H26" s="4"/>
+    </row>
+    <row r="27" ht="36.0" customHeight="1">
+      <c r="D27" s="5" t="s">
+        <v>4</v>
+      </c>
+      <c r="E27" s="6" t="s">
+        <v>5</v>
+      </c>
+      <c r="F27" s="6" t="s">
         <v>26</v>
       </c>
-      <c r="H25" s="3"/>
-    </row>
-    <row r="26" ht="36.0" customHeight="1">
-      <c r="D26" s="6" t="s">
-        <v>16</v>
-      </c>
-      <c r="E26" s="1" t="s">
-        <v>17</v>
-      </c>
-      <c r="F26" s="5" t="s">
-        <v>22</v>
-      </c>
-      <c r="G26" s="1" t="s">
-        <v>23</v>
-      </c>
-      <c r="H26" s="4"/>
-    </row>
-    <row r="27" ht="36.0" customHeight="1">
-      <c r="D27" s="6" t="s">
-        <v>20</v>
-      </c>
-      <c r="E27" s="1" t="s">
-        <v>21</v>
-      </c>
-      <c r="F27" s="5" t="s">
-        <v>27</v>
-      </c>
       <c r="G27" s="1" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="H27" s="4"/>
     </row>
@@ -827,22 +830,22 @@
         <v>1</v>
       </c>
       <c r="F29" s="1" t="s">
+        <v>11</v>
+      </c>
+      <c r="G29" s="3" t="s">
         <v>14</v>
       </c>
-      <c r="G29" s="3" t="s">
-        <v>19</v>
-      </c>
       <c r="H29" s="4"/>
     </row>
     <row r="30" ht="36.0" customHeight="1">
-      <c r="D30" s="1" t="s">
-        <v>4</v>
-      </c>
-      <c r="E30" s="1" t="s">
-        <v>5</v>
-      </c>
-      <c r="F30" s="5" t="s">
-        <v>10</v>
+      <c r="D30" s="5" t="s">
+        <v>4</v>
+      </c>
+      <c r="E30" s="6" t="s">
+        <v>5</v>
+      </c>
+      <c r="F30" s="6" t="s">
+        <v>2</v>
       </c>
       <c r="G30" s="1" t="s">
         <v>7</v>
@@ -856,71 +859,71 @@
       <c r="E31" s="1" t="s">
         <v>9</v>
       </c>
-      <c r="F31" s="5" t="s">
+      <c r="F31" s="6" t="s">
         <v>6</v>
       </c>
-      <c r="G31" s="5" t="s">
-        <v>15</v>
+      <c r="G31" s="6" t="s">
+        <v>12</v>
       </c>
       <c r="H31" s="4"/>
     </row>
     <row r="32" ht="36.0" customHeight="1">
-      <c r="D32" s="6" t="s">
+      <c r="D32" s="7" t="s">
+        <v>23</v>
+      </c>
+      <c r="E32" s="1" t="s">
+        <v>24</v>
+      </c>
+      <c r="F32" s="2" t="s">
+        <v>2</v>
+      </c>
+      <c r="G32" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="H32" s="4"/>
+    </row>
+    <row r="33" ht="36.0" customHeight="1">
+      <c r="D33" s="5" t="s">
+        <v>4</v>
+      </c>
+      <c r="E33" s="6" t="s">
+        <v>5</v>
+      </c>
+      <c r="F33" s="6" t="s">
+        <v>17</v>
+      </c>
+      <c r="G33" s="1" t="s">
+        <v>10</v>
+      </c>
+      <c r="H33" s="4"/>
+    </row>
+    <row r="34" ht="36.0" customHeight="1">
+      <c r="D34" s="5" t="s">
+        <v>4</v>
+      </c>
+      <c r="E34" s="6" t="s">
+        <v>5</v>
+      </c>
+      <c r="F34" s="6" t="s">
+        <v>2</v>
+      </c>
+      <c r="G34" s="6" t="s">
         <v>12</v>
       </c>
-      <c r="E32" s="1" t="s">
-        <v>13</v>
-      </c>
-      <c r="F32" s="2" t="s">
-        <v>2</v>
-      </c>
-      <c r="G32" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="H32" s="4"/>
-    </row>
-    <row r="33" ht="36.0" customHeight="1">
-      <c r="D33" s="6" t="s">
-        <v>16</v>
-      </c>
-      <c r="E33" s="1" t="s">
-        <v>17</v>
-      </c>
-      <c r="F33" s="5" t="s">
-        <v>22</v>
-      </c>
-      <c r="G33" s="1" t="s">
-        <v>11</v>
-      </c>
-      <c r="H33" s="4"/>
-    </row>
-    <row r="34" ht="36.0" customHeight="1">
-      <c r="D34" s="6" t="s">
+      <c r="H34" s="4"/>
+    </row>
+    <row r="35" ht="36.0" customHeight="1">
+      <c r="D35" s="5" t="s">
+        <v>4</v>
+      </c>
+      <c r="E35" s="6" t="s">
+        <v>5</v>
+      </c>
+      <c r="F35" s="2" t="s">
         <v>20</v>
       </c>
-      <c r="E34" s="1" t="s">
-        <v>21</v>
-      </c>
-      <c r="F34" s="5" t="s">
-        <v>10</v>
-      </c>
-      <c r="G34" s="5" t="s">
-        <v>15</v>
-      </c>
-      <c r="H34" s="4"/>
-    </row>
-    <row r="35" ht="36.0" customHeight="1">
-      <c r="D35" s="1" t="s">
-        <v>8</v>
-      </c>
-      <c r="E35" s="1" t="s">
-        <v>9</v>
-      </c>
-      <c r="F35" s="2" t="s">
-        <v>2</v>
-      </c>
       <c r="G35" s="3" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="H35" s="3"/>
     </row>
@@ -941,16 +944,16 @@
     </row>
     <row r="37" ht="36.0" customHeight="1">
       <c r="D37" s="1" t="s">
-        <v>4</v>
+        <v>21</v>
       </c>
       <c r="E37" s="1" t="s">
-        <v>5</v>
+        <v>22</v>
       </c>
       <c r="F37" s="1" t="s">
+        <v>11</v>
+      </c>
+      <c r="G37" s="3" t="s">
         <v>14</v>
-      </c>
-      <c r="G37" s="3" t="s">
-        <v>19</v>
       </c>
       <c r="H37" s="4"/>
     </row>
@@ -961,8 +964,8 @@
       <c r="E38" s="1" t="s">
         <v>9</v>
       </c>
-      <c r="F38" s="5" t="s">
-        <v>22</v>
+      <c r="F38" s="6" t="s">
+        <v>17</v>
       </c>
       <c r="G38" s="1" t="s">
         <v>7</v>
@@ -970,59 +973,59 @@
       <c r="H38" s="4"/>
     </row>
     <row r="39" ht="36.0" customHeight="1">
-      <c r="D39" s="6" t="s">
-        <v>12</v>
+      <c r="D39" s="7" t="s">
+        <v>23</v>
       </c>
       <c r="E39" s="1" t="s">
+        <v>24</v>
+      </c>
+      <c r="F39" s="2" t="s">
+        <v>20</v>
+      </c>
+      <c r="G39" s="1" t="s">
+        <v>10</v>
+      </c>
+      <c r="H39" s="4"/>
+    </row>
+    <row r="40" ht="36.0" customHeight="1">
+      <c r="D40" s="5" t="s">
+        <v>4</v>
+      </c>
+      <c r="E40" s="6" t="s">
+        <v>5</v>
+      </c>
+      <c r="F40" s="2" t="s">
+        <v>2</v>
+      </c>
+      <c r="G40" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="H40" s="4"/>
+    </row>
+    <row r="41" ht="36.0" customHeight="1">
+      <c r="D41" s="5" t="s">
+        <v>4</v>
+      </c>
+      <c r="E41" s="6" t="s">
+        <v>5</v>
+      </c>
+      <c r="F41" s="3" t="s">
         <v>13</v>
       </c>
-      <c r="F39" s="2" t="s">
-        <v>2</v>
-      </c>
-      <c r="G39" s="1" t="s">
-        <v>11</v>
-      </c>
-      <c r="H39" s="4"/>
-    </row>
-    <row r="40" ht="36.0" customHeight="1">
-      <c r="D40" s="6" t="s">
-        <v>16</v>
-      </c>
-      <c r="E40" s="1" t="s">
-        <v>17</v>
-      </c>
-      <c r="F40" s="2" t="s">
-        <v>2</v>
-      </c>
-      <c r="G40" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="H40" s="4"/>
-    </row>
-    <row r="41" ht="36.0" customHeight="1">
-      <c r="D41" s="6" t="s">
-        <v>20</v>
-      </c>
-      <c r="E41" s="1" t="s">
-        <v>21</v>
-      </c>
-      <c r="F41" s="3" t="s">
-        <v>18</v>
-      </c>
       <c r="G41" s="3" t="s">
-        <v>19</v>
+        <v>14</v>
       </c>
       <c r="H41" s="4"/>
     </row>
     <row r="42" ht="36.0" customHeight="1">
-      <c r="D42" s="1" t="s">
-        <v>8</v>
-      </c>
-      <c r="E42" s="1" t="s">
-        <v>9</v>
-      </c>
-      <c r="F42" s="5" t="s">
-        <v>10</v>
+      <c r="D42" s="5" t="s">
+        <v>4</v>
+      </c>
+      <c r="E42" s="6" t="s">
+        <v>5</v>
+      </c>
+      <c r="F42" s="6" t="s">
+        <v>2</v>
       </c>
       <c r="G42" s="1" t="s">
         <v>7</v>
@@ -1046,16 +1049,16 @@
     </row>
     <row r="44" ht="36.0" customHeight="1">
       <c r="D44" s="1" t="s">
-        <v>4</v>
+        <v>21</v>
       </c>
       <c r="E44" s="1" t="s">
-        <v>5</v>
-      </c>
-      <c r="F44" s="5" t="s">
-        <v>14</v>
+        <v>22</v>
+      </c>
+      <c r="F44" s="6" t="s">
+        <v>11</v>
       </c>
       <c r="G44" s="1" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="H44" s="4"/>
     </row>
@@ -1067,7 +1070,7 @@
         <v>9</v>
       </c>
       <c r="F45" s="1" t="s">
-        <v>14</v>
+        <v>11</v>
       </c>
       <c r="G45" s="1" t="s">
         <v>7</v>
@@ -1075,56 +1078,56 @@
       <c r="H45" s="4"/>
     </row>
     <row r="46" ht="36.0" customHeight="1">
-      <c r="D46" s="6" t="s">
-        <v>12</v>
+      <c r="D46" s="7" t="s">
+        <v>23</v>
       </c>
       <c r="E46" s="1" t="s">
-        <v>13</v>
-      </c>
-      <c r="F46" s="5" t="s">
-        <v>22</v>
+        <v>24</v>
+      </c>
+      <c r="F46" s="6" t="s">
+        <v>17</v>
       </c>
       <c r="G46" s="1" t="s">
-        <v>23</v>
+        <v>18</v>
       </c>
       <c r="H46" s="4"/>
     </row>
     <row r="47" ht="36.0" customHeight="1">
-      <c r="D47" s="6" t="s">
-        <v>16</v>
-      </c>
-      <c r="E47" s="1" t="s">
-        <v>17</v>
-      </c>
-      <c r="F47" s="5" t="s">
-        <v>10</v>
+      <c r="D47" s="5" t="s">
+        <v>4</v>
+      </c>
+      <c r="E47" s="6" t="s">
+        <v>5</v>
+      </c>
+      <c r="F47" s="6" t="s">
+        <v>2</v>
       </c>
       <c r="G47" s="1" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="H47" s="4"/>
     </row>
     <row r="48" ht="36.0" customHeight="1">
-      <c r="D48" s="6" t="s">
-        <v>20</v>
-      </c>
-      <c r="E48" s="1" t="s">
-        <v>21</v>
+      <c r="D48" s="5" t="s">
+        <v>4</v>
+      </c>
+      <c r="E48" s="6" t="s">
+        <v>5</v>
       </c>
       <c r="F48" s="2" t="s">
-        <v>10</v>
+        <v>2</v>
       </c>
       <c r="G48" s="3" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="H48" s="3"/>
     </row>
     <row r="49" ht="36.0" customHeight="1">
-      <c r="D49" s="1" t="s">
-        <v>8</v>
-      </c>
-      <c r="E49" s="1" t="s">
-        <v>9</v>
+      <c r="D49" s="5" t="s">
+        <v>4</v>
+      </c>
+      <c r="E49" s="6" t="s">
+        <v>5</v>
       </c>
       <c r="F49" s="2" t="s">
         <v>2</v>
@@ -1141,20 +1144,20 @@
       <c r="E50" s="1" t="s">
         <v>1</v>
       </c>
-      <c r="F50" s="5" t="s">
-        <v>22</v>
+      <c r="F50" s="6" t="s">
+        <v>17</v>
       </c>
       <c r="G50" s="1" t="s">
-        <v>23</v>
+        <v>18</v>
       </c>
       <c r="H50" s="4"/>
     </row>
     <row r="51" ht="36.0" customHeight="1">
       <c r="D51" s="1" t="s">
-        <v>4</v>
+        <v>21</v>
       </c>
       <c r="E51" s="1" t="s">
-        <v>5</v>
+        <v>22</v>
       </c>
       <c r="F51" s="2" t="s">
         <v>2</v>
@@ -1171,23 +1174,23 @@
       <c r="E52" s="1" t="s">
         <v>9</v>
       </c>
-      <c r="F52" s="5" t="s">
-        <v>22</v>
+      <c r="F52" s="6" t="s">
+        <v>17</v>
       </c>
       <c r="G52" s="1" t="s">
+        <v>18</v>
+      </c>
+      <c r="H52" s="4"/>
+    </row>
+    <row r="53" ht="36.0" customHeight="1">
+      <c r="D53" s="7" t="s">
         <v>23</v>
       </c>
-      <c r="H52" s="4"/>
-    </row>
-    <row r="53" ht="36.0" customHeight="1">
-      <c r="D53" s="6" t="s">
-        <v>12</v>
-      </c>
       <c r="E53" s="1" t="s">
-        <v>13</v>
+        <v>24</v>
       </c>
       <c r="F53" s="1" t="s">
-        <v>14</v>
+        <v>11</v>
       </c>
       <c r="G53" s="1" t="s">
         <v>7</v>
@@ -1195,11 +1198,11 @@
       <c r="H53" s="4"/>
     </row>
     <row r="54" ht="36.0" customHeight="1">
-      <c r="D54" s="6" t="s">
-        <v>16</v>
-      </c>
-      <c r="E54" s="1" t="s">
-        <v>17</v>
+      <c r="D54" s="5" t="s">
+        <v>4</v>
+      </c>
+      <c r="E54" s="6" t="s">
+        <v>5</v>
       </c>
       <c r="F54" s="2" t="s">
         <v>2</v>
@@ -1210,29 +1213,29 @@
       <c r="H54" s="4"/>
     </row>
     <row r="55" ht="36.0" customHeight="1">
-      <c r="D55" s="6" t="s">
-        <v>20</v>
-      </c>
-      <c r="E55" s="1" t="s">
-        <v>21</v>
+      <c r="D55" s="5" t="s">
+        <v>4</v>
+      </c>
+      <c r="E55" s="6" t="s">
+        <v>5</v>
       </c>
       <c r="F55" s="1" t="s">
+        <v>11</v>
+      </c>
+      <c r="G55" s="3" t="s">
         <v>14</v>
       </c>
-      <c r="G55" s="3" t="s">
-        <v>19</v>
-      </c>
       <c r="H55" s="4"/>
     </row>
     <row r="56" ht="36.0" customHeight="1">
-      <c r="D56" s="1" t="s">
-        <v>8</v>
-      </c>
-      <c r="E56" s="1" t="s">
-        <v>9</v>
-      </c>
-      <c r="F56" s="5" t="s">
-        <v>22</v>
+      <c r="D56" s="5" t="s">
+        <v>4</v>
+      </c>
+      <c r="E56" s="6" t="s">
+        <v>5</v>
+      </c>
+      <c r="F56" s="6" t="s">
+        <v>17</v>
       </c>
       <c r="G56" s="1" t="s">
         <v>7</v>
@@ -1246,23 +1249,23 @@
       <c r="E57" s="1" t="s">
         <v>1</v>
       </c>
-      <c r="F57" s="5" t="s">
-        <v>22</v>
+      <c r="F57" s="6" t="s">
+        <v>17</v>
       </c>
       <c r="G57" s="1" t="s">
-        <v>23</v>
+        <v>18</v>
       </c>
       <c r="H57" s="4"/>
     </row>
     <row r="58" ht="36.0" customHeight="1">
       <c r="D58" s="1" t="s">
-        <v>4</v>
+        <v>21</v>
       </c>
       <c r="E58" s="1" t="s">
-        <v>5</v>
-      </c>
-      <c r="F58" s="5" t="s">
-        <v>27</v>
+        <v>22</v>
+      </c>
+      <c r="F58" s="6" t="s">
+        <v>26</v>
       </c>
       <c r="G58" s="1" t="s">
         <v>7</v>
@@ -1285,47 +1288,47 @@
       <c r="H59" s="4"/>
     </row>
     <row r="60" ht="36.0" customHeight="1">
-      <c r="D60" s="6" t="s">
-        <v>12</v>
+      <c r="D60" s="7" t="s">
+        <v>23</v>
       </c>
       <c r="E60" s="1" t="s">
-        <v>13</v>
-      </c>
-      <c r="F60" s="5" t="s">
+        <v>24</v>
+      </c>
+      <c r="F60" s="6" t="s">
+        <v>11</v>
+      </c>
+      <c r="G60" s="1" t="s">
+        <v>10</v>
+      </c>
+      <c r="H60" s="4"/>
+    </row>
+    <row r="61" ht="36.0" customHeight="1">
+      <c r="D61" s="5" t="s">
+        <v>4</v>
+      </c>
+      <c r="E61" s="6" t="s">
+        <v>5</v>
+      </c>
+      <c r="F61" s="1" t="s">
+        <v>11</v>
+      </c>
+      <c r="G61" s="3" t="s">
         <v>14</v>
       </c>
-      <c r="G60" s="1" t="s">
-        <v>11</v>
-      </c>
-      <c r="H60" s="4"/>
-    </row>
-    <row r="61" ht="36.0" customHeight="1">
-      <c r="D61" s="6" t="s">
-        <v>16</v>
-      </c>
-      <c r="E61" s="1" t="s">
-        <v>17</v>
-      </c>
-      <c r="F61" s="1" t="s">
-        <v>14</v>
-      </c>
-      <c r="G61" s="3" t="s">
-        <v>19</v>
-      </c>
       <c r="H61" s="4"/>
     </row>
     <row r="62" ht="36.0" customHeight="1">
-      <c r="D62" s="6" t="s">
-        <v>20</v>
-      </c>
-      <c r="E62" s="1" t="s">
-        <v>21</v>
-      </c>
-      <c r="F62" s="5" t="s">
-        <v>22</v>
+      <c r="D62" s="5" t="s">
+        <v>4</v>
+      </c>
+      <c r="E62" s="6" t="s">
+        <v>5</v>
+      </c>
+      <c r="F62" s="6" t="s">
+        <v>17</v>
       </c>
       <c r="G62" s="1" t="s">
-        <v>23</v>
+        <v>18</v>
       </c>
       <c r="H62" s="4"/>
     </row>
@@ -1336,11 +1339,11 @@
       <c r="E63" s="1" t="s">
         <v>9</v>
       </c>
-      <c r="F63" s="5" t="s">
-        <v>22</v>
+      <c r="F63" s="6" t="s">
+        <v>17</v>
       </c>
       <c r="G63" s="1" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="H63" s="4"/>
     </row>
@@ -1352,7 +1355,7 @@
         <v>1</v>
       </c>
       <c r="F64" s="1" t="s">
-        <v>14</v>
+        <v>11</v>
       </c>
       <c r="G64" s="1" t="s">
         <v>7</v>
@@ -1361,10 +1364,10 @@
     </row>
     <row r="65" ht="36.0" customHeight="1">
       <c r="D65" s="1" t="s">
-        <v>4</v>
+        <v>21</v>
       </c>
       <c r="E65" s="1" t="s">
-        <v>5</v>
+        <v>22</v>
       </c>
       <c r="F65" s="2" t="s">
         <v>2</v>
@@ -1375,41 +1378,41 @@
       <c r="H65" s="4"/>
     </row>
     <row r="66" ht="36.0" customHeight="1">
-      <c r="D66" s="1" t="s">
-        <v>8</v>
-      </c>
-      <c r="E66" s="1" t="s">
-        <v>9</v>
+      <c r="D66" s="5" t="s">
+        <v>4</v>
+      </c>
+      <c r="E66" s="6" t="s">
+        <v>5</v>
       </c>
       <c r="F66" s="1" t="s">
+        <v>11</v>
+      </c>
+      <c r="G66" s="3" t="s">
+        <v>25</v>
+      </c>
+      <c r="H66" s="3"/>
+    </row>
+    <row r="67" ht="36.0" customHeight="1">
+      <c r="D67" s="7" t="s">
+        <v>23</v>
+      </c>
+      <c r="E67" s="1" t="s">
+        <v>24</v>
+      </c>
+      <c r="F67" s="3" t="s">
+        <v>13</v>
+      </c>
+      <c r="G67" s="3" t="s">
         <v>14</v>
       </c>
-      <c r="G66" s="3" t="s">
-        <v>26</v>
-      </c>
-      <c r="H66" s="3"/>
-    </row>
-    <row r="67" ht="36.0" customHeight="1">
-      <c r="D67" s="6" t="s">
-        <v>12</v>
-      </c>
-      <c r="E67" s="1" t="s">
-        <v>13</v>
-      </c>
-      <c r="F67" s="3" t="s">
-        <v>18</v>
-      </c>
-      <c r="G67" s="3" t="s">
-        <v>19</v>
-      </c>
       <c r="H67" s="4"/>
     </row>
     <row r="68" ht="36.0" customHeight="1">
-      <c r="D68" s="6" t="s">
-        <v>16</v>
-      </c>
-      <c r="E68" s="1" t="s">
-        <v>17</v>
+      <c r="D68" s="5" t="s">
+        <v>4</v>
+      </c>
+      <c r="E68" s="6" t="s">
+        <v>5</v>
       </c>
       <c r="F68" s="2" t="s">
         <v>2</v>
@@ -1420,17 +1423,17 @@
       <c r="H68" s="4"/>
     </row>
     <row r="69" ht="36.0" customHeight="1">
-      <c r="D69" s="6" t="s">
-        <v>20</v>
-      </c>
-      <c r="E69" s="1" t="s">
-        <v>21</v>
-      </c>
-      <c r="F69" s="5" t="s">
-        <v>22</v>
+      <c r="D69" s="5" t="s">
+        <v>4</v>
+      </c>
+      <c r="E69" s="6" t="s">
+        <v>5</v>
+      </c>
+      <c r="F69" s="6" t="s">
+        <v>17</v>
       </c>
       <c r="G69" s="1" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="H69" s="4"/>
     </row>
@@ -1442,7 +1445,7 @@
         <v>9</v>
       </c>
       <c r="F70" s="1" t="s">
-        <v>14</v>
+        <v>11</v>
       </c>
       <c r="G70" s="1" t="s">
         <v>7</v>
@@ -1457,34 +1460,34 @@
         <v>1</v>
       </c>
       <c r="F71" s="3" t="s">
-        <v>18</v>
+        <v>13</v>
       </c>
       <c r="G71" s="3" t="s">
-        <v>19</v>
+        <v>14</v>
       </c>
       <c r="H71" s="4"/>
     </row>
     <row r="72" ht="36.0" customHeight="1">
       <c r="D72" s="1" t="s">
-        <v>4</v>
+        <v>21</v>
       </c>
       <c r="E72" s="1" t="s">
-        <v>5</v>
-      </c>
-      <c r="F72" s="5" t="s">
-        <v>10</v>
+        <v>22</v>
+      </c>
+      <c r="F72" s="6" t="s">
+        <v>2</v>
       </c>
       <c r="G72" s="1" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="H72" s="4"/>
     </row>
     <row r="73" ht="36.0" customHeight="1">
-      <c r="D73" s="1" t="s">
-        <v>8</v>
-      </c>
-      <c r="E73" s="1" t="s">
-        <v>9</v>
+      <c r="D73" s="5" t="s">
+        <v>4</v>
+      </c>
+      <c r="E73" s="6" t="s">
+        <v>5</v>
       </c>
       <c r="F73" s="2" t="s">
         <v>2</v>
@@ -1495,62 +1498,62 @@
       <c r="H73" s="4"/>
     </row>
     <row r="74" ht="36.0" customHeight="1">
-      <c r="D74" s="6" t="s">
-        <v>12</v>
+      <c r="D74" s="7" t="s">
+        <v>23</v>
       </c>
       <c r="E74" s="1" t="s">
+        <v>24</v>
+      </c>
+      <c r="F74" s="6" t="s">
+        <v>26</v>
+      </c>
+      <c r="G74" s="1" t="s">
+        <v>10</v>
+      </c>
+      <c r="H74" s="4"/>
+    </row>
+    <row r="75" ht="36.0" customHeight="1">
+      <c r="D75" s="5" t="s">
+        <v>4</v>
+      </c>
+      <c r="E75" s="6" t="s">
+        <v>5</v>
+      </c>
+      <c r="F75" s="6" t="s">
+        <v>17</v>
+      </c>
+      <c r="G75" s="1" t="s">
+        <v>18</v>
+      </c>
+      <c r="H75" s="4"/>
+    </row>
+    <row r="76" ht="36.0" customHeight="1">
+      <c r="D76" s="5" t="s">
+        <v>4</v>
+      </c>
+      <c r="E76" s="6" t="s">
+        <v>5</v>
+      </c>
+      <c r="F76" s="2" t="s">
+        <v>2</v>
+      </c>
+      <c r="G76" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="H76" s="4"/>
+    </row>
+    <row r="77" ht="36.0" customHeight="1">
+      <c r="D77" s="5" t="s">
+        <v>4</v>
+      </c>
+      <c r="E77" s="6" t="s">
+        <v>5</v>
+      </c>
+      <c r="F77" s="3" t="s">
         <v>13</v>
       </c>
-      <c r="F74" s="5" t="s">
-        <v>27</v>
-      </c>
-      <c r="G74" s="1" t="s">
-        <v>11</v>
-      </c>
-      <c r="H74" s="4"/>
-    </row>
-    <row r="75" ht="36.0" customHeight="1">
-      <c r="D75" s="6" t="s">
-        <v>16</v>
-      </c>
-      <c r="E75" s="1" t="s">
-        <v>17</v>
-      </c>
-      <c r="F75" s="5" t="s">
-        <v>22</v>
-      </c>
-      <c r="G75" s="1" t="s">
-        <v>23</v>
-      </c>
-      <c r="H75" s="4"/>
-    </row>
-    <row r="76" ht="36.0" customHeight="1">
-      <c r="D76" s="6" t="s">
-        <v>20</v>
-      </c>
-      <c r="E76" s="1" t="s">
-        <v>21</v>
-      </c>
-      <c r="F76" s="2" t="s">
-        <v>2</v>
-      </c>
-      <c r="G76" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="H76" s="4"/>
-    </row>
-    <row r="77" ht="36.0" customHeight="1">
-      <c r="D77" s="1" t="s">
-        <v>8</v>
-      </c>
-      <c r="E77" s="1" t="s">
-        <v>9</v>
-      </c>
-      <c r="F77" s="3" t="s">
-        <v>18</v>
-      </c>
       <c r="G77" s="3" t="s">
-        <v>19</v>
+        <v>14</v>
       </c>
       <c r="H77" s="4"/>
     </row>
@@ -1561,8 +1564,8 @@
       <c r="E78" s="1" t="s">
         <v>1</v>
       </c>
-      <c r="F78" s="5" t="s">
-        <v>27</v>
+      <c r="F78" s="6" t="s">
+        <v>26</v>
       </c>
       <c r="G78" s="1" t="s">
         <v>7</v>
@@ -1571,16 +1574,16 @@
     </row>
     <row r="79" ht="36.0" customHeight="1">
       <c r="D79" s="1" t="s">
-        <v>4</v>
+        <v>21</v>
       </c>
       <c r="E79" s="1" t="s">
-        <v>5</v>
-      </c>
-      <c r="F79" s="5" t="s">
-        <v>14</v>
+        <v>22</v>
+      </c>
+      <c r="F79" s="6" t="s">
+        <v>11</v>
       </c>
       <c r="G79" s="1" t="s">
-        <v>23</v>
+        <v>18</v>
       </c>
       <c r="H79" s="4"/>
     </row>
@@ -1592,21 +1595,21 @@
         <v>9</v>
       </c>
       <c r="F80" s="2" t="s">
-        <v>2</v>
+        <v>20</v>
       </c>
       <c r="G80" s="1" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="H80" s="4"/>
     </row>
     <row r="81" ht="36.0" customHeight="1">
-      <c r="D81" s="6" t="s">
-        <v>12</v>
+      <c r="D81" s="7" t="s">
+        <v>23</v>
       </c>
       <c r="E81" s="1" t="s">
-        <v>13</v>
-      </c>
-      <c r="F81" s="5" t="s">
+        <v>24</v>
+      </c>
+      <c r="F81" s="6" t="s">
         <v>6</v>
       </c>
       <c r="G81" s="1" t="s">
@@ -1615,11 +1618,11 @@
       <c r="H81" s="4"/>
     </row>
     <row r="82" ht="36.0" customHeight="1">
-      <c r="D82" s="6" t="s">
-        <v>16</v>
-      </c>
-      <c r="E82" s="1" t="s">
-        <v>17</v>
+      <c r="D82" s="5" t="s">
+        <v>4</v>
+      </c>
+      <c r="E82" s="6" t="s">
+        <v>5</v>
       </c>
       <c r="F82" s="2" t="s">
         <v>2</v>
@@ -1630,17 +1633,17 @@
       <c r="H82" s="4"/>
     </row>
     <row r="83" ht="36.0" customHeight="1">
-      <c r="D83" s="6" t="s">
-        <v>20</v>
-      </c>
-      <c r="E83" s="1" t="s">
-        <v>21</v>
-      </c>
-      <c r="F83" s="5" t="s">
-        <v>22</v>
+      <c r="D83" s="5" t="s">
+        <v>4</v>
+      </c>
+      <c r="E83" s="6" t="s">
+        <v>5</v>
+      </c>
+      <c r="F83" s="6" t="s">
+        <v>17</v>
       </c>
       <c r="G83" s="1" t="s">
-        <v>23</v>
+        <v>18</v>
       </c>
       <c r="H83" s="4"/>
     </row>
@@ -1652,7 +1655,7 @@
         <v>9</v>
       </c>
       <c r="F84" s="2" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="G84" s="1" t="s">
         <v>7</v>
@@ -1676,28 +1679,28 @@
     </row>
     <row r="86" ht="36.0" customHeight="1">
       <c r="D86" s="1" t="s">
-        <v>4</v>
+        <v>21</v>
       </c>
       <c r="E86" s="1" t="s">
-        <v>5</v>
-      </c>
-      <c r="F86" s="5" t="s">
-        <v>14</v>
+        <v>22</v>
+      </c>
+      <c r="F86" s="6" t="s">
+        <v>11</v>
       </c>
       <c r="G86" s="1" t="s">
-        <v>23</v>
+        <v>18</v>
       </c>
       <c r="H86" s="4"/>
     </row>
     <row r="87" ht="36.0" customHeight="1">
-      <c r="D87" s="1" t="s">
-        <v>8</v>
-      </c>
-      <c r="E87" s="1" t="s">
-        <v>9</v>
+      <c r="D87" s="5" t="s">
+        <v>4</v>
+      </c>
+      <c r="E87" s="6" t="s">
+        <v>5</v>
       </c>
       <c r="F87" s="2" t="s">
-        <v>2</v>
+        <v>20</v>
       </c>
       <c r="G87" s="1" t="s">
         <v>7</v>
@@ -1705,47 +1708,47 @@
       <c r="H87" s="4"/>
     </row>
     <row r="88" ht="36.0" customHeight="1">
-      <c r="D88" s="6" t="s">
+      <c r="D88" s="7" t="s">
+        <v>23</v>
+      </c>
+      <c r="E88" s="1" t="s">
+        <v>24</v>
+      </c>
+      <c r="F88" s="2" t="s">
+        <v>2</v>
+      </c>
+      <c r="G88" s="1" t="s">
+        <v>10</v>
+      </c>
+      <c r="H88" s="4"/>
+    </row>
+    <row r="89" ht="36.0" customHeight="1">
+      <c r="D89" s="5" t="s">
+        <v>4</v>
+      </c>
+      <c r="E89" s="6" t="s">
+        <v>5</v>
+      </c>
+      <c r="F89" s="6" t="s">
+        <v>2</v>
+      </c>
+      <c r="G89" s="6" t="s">
         <v>12</v>
       </c>
-      <c r="E88" s="1" t="s">
+      <c r="H89" s="4"/>
+    </row>
+    <row r="90" ht="36.0" customHeight="1">
+      <c r="D90" s="5" t="s">
+        <v>4</v>
+      </c>
+      <c r="E90" s="6" t="s">
+        <v>5</v>
+      </c>
+      <c r="F90" s="3" t="s">
         <v>13</v>
       </c>
-      <c r="F88" s="2" t="s">
-        <v>10</v>
-      </c>
-      <c r="G88" s="1" t="s">
-        <v>11</v>
-      </c>
-      <c r="H88" s="4"/>
-    </row>
-    <row r="89" ht="36.0" customHeight="1">
-      <c r="D89" s="6" t="s">
-        <v>16</v>
-      </c>
-      <c r="E89" s="1" t="s">
-        <v>17</v>
-      </c>
-      <c r="F89" s="5" t="s">
-        <v>10</v>
-      </c>
-      <c r="G89" s="5" t="s">
-        <v>15</v>
-      </c>
-      <c r="H89" s="4"/>
-    </row>
-    <row r="90" ht="36.0" customHeight="1">
-      <c r="D90" s="6" t="s">
-        <v>20</v>
-      </c>
-      <c r="E90" s="1" t="s">
-        <v>21</v>
-      </c>
-      <c r="F90" s="3" t="s">
-        <v>18</v>
-      </c>
       <c r="G90" s="3" t="s">
-        <v>19</v>
+        <v>14</v>
       </c>
       <c r="H90" s="4"/>
     </row>
@@ -1757,10 +1760,10 @@
         <v>9</v>
       </c>
       <c r="F91" s="2" t="s">
-        <v>2</v>
+        <v>20</v>
       </c>
       <c r="G91" s="1" t="s">
-        <v>23</v>
+        <v>18</v>
       </c>
       <c r="H91" s="4"/>
     </row>
@@ -1771,20 +1774,20 @@
       <c r="E92" s="1" t="s">
         <v>1</v>
       </c>
-      <c r="F92" s="5" t="s">
-        <v>10</v>
+      <c r="F92" s="6" t="s">
+        <v>2</v>
       </c>
       <c r="G92" s="3" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="H92" s="3"/>
     </row>
     <row r="93" ht="36.0" customHeight="1">
       <c r="D93" s="1" t="s">
-        <v>4</v>
+        <v>21</v>
       </c>
       <c r="E93" s="1" t="s">
-        <v>5</v>
+        <v>22</v>
       </c>
       <c r="F93" s="2" t="s">
         <v>2</v>
@@ -1801,38 +1804,38 @@
       <c r="E94" s="1" t="s">
         <v>9</v>
       </c>
-      <c r="F94" s="5" t="s">
-        <v>14</v>
+      <c r="F94" s="6" t="s">
+        <v>11</v>
       </c>
       <c r="G94" s="1" t="s">
-        <v>23</v>
+        <v>18</v>
       </c>
       <c r="H94" s="4"/>
     </row>
     <row r="95" ht="36.0" customHeight="1">
-      <c r="D95" s="6" t="s">
-        <v>12</v>
-      </c>
-      <c r="E95" s="1" t="s">
-        <v>13</v>
+      <c r="D95" s="5" t="s">
+        <v>4</v>
+      </c>
+      <c r="E95" s="6" t="s">
+        <v>5</v>
       </c>
       <c r="F95" s="2" t="s">
-        <v>10</v>
+        <v>2</v>
       </c>
       <c r="G95" s="1" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="H95" s="4"/>
     </row>
     <row r="96" ht="36.0" customHeight="1">
-      <c r="D96" s="6" t="s">
-        <v>16</v>
-      </c>
-      <c r="E96" s="1" t="s">
-        <v>17</v>
+      <c r="D96" s="5" t="s">
+        <v>4</v>
+      </c>
+      <c r="E96" s="6" t="s">
+        <v>5</v>
       </c>
       <c r="F96" s="2" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="G96" s="1" t="s">
         <v>7</v>
@@ -1840,17 +1843,17 @@
       <c r="H96" s="4"/>
     </row>
     <row r="97" ht="36.0" customHeight="1">
-      <c r="D97" s="6" t="s">
-        <v>20</v>
-      </c>
-      <c r="E97" s="1" t="s">
-        <v>21</v>
+      <c r="D97" s="5" t="s">
+        <v>4</v>
+      </c>
+      <c r="E97" s="6" t="s">
+        <v>5</v>
       </c>
       <c r="F97" s="1" t="s">
-        <v>14</v>
-      </c>
-      <c r="G97" s="5" t="s">
-        <v>15</v>
+        <v>11</v>
+      </c>
+      <c r="G97" s="6" t="s">
+        <v>12</v>
       </c>
       <c r="H97" s="4"/>
     </row>
@@ -1861,11 +1864,11 @@
       <c r="E98" s="1" t="s">
         <v>9</v>
       </c>
-      <c r="F98" s="5" t="s">
-        <v>14</v>
+      <c r="F98" s="6" t="s">
+        <v>11</v>
       </c>
       <c r="G98" s="1" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="H98" s="4"/>
     </row>
@@ -1886,43 +1889,43 @@
     </row>
     <row r="100" ht="36.0" customHeight="1">
       <c r="D100" s="1" t="s">
-        <v>4</v>
+        <v>21</v>
       </c>
       <c r="E100" s="1" t="s">
-        <v>5</v>
-      </c>
-      <c r="F100" s="5" t="s">
-        <v>14</v>
+        <v>22</v>
+      </c>
+      <c r="F100" s="6" t="s">
+        <v>11</v>
       </c>
       <c r="G100" s="1" t="s">
+        <v>18</v>
+      </c>
+      <c r="H100" s="4"/>
+    </row>
+    <row r="101" ht="36.0" customHeight="1">
+      <c r="D101" s="5" t="s">
+        <v>4</v>
+      </c>
+      <c r="E101" s="6" t="s">
+        <v>5</v>
+      </c>
+      <c r="F101" s="6" t="s">
+        <v>17</v>
+      </c>
+      <c r="G101" s="1" t="s">
+        <v>10</v>
+      </c>
+      <c r="H101" s="4"/>
+    </row>
+    <row r="102" ht="36.0" customHeight="1">
+      <c r="D102" s="7" t="s">
         <v>23</v>
       </c>
-      <c r="H100" s="4"/>
-    </row>
-    <row r="101" ht="36.0" customHeight="1">
-      <c r="D101" s="1" t="s">
-        <v>8</v>
-      </c>
-      <c r="E101" s="1" t="s">
-        <v>9</v>
-      </c>
-      <c r="F101" s="5" t="s">
-        <v>22</v>
-      </c>
-      <c r="G101" s="1" t="s">
-        <v>11</v>
-      </c>
-      <c r="H101" s="4"/>
-    </row>
-    <row r="102" ht="36.0" customHeight="1">
-      <c r="D102" s="6" t="s">
-        <v>12</v>
-      </c>
       <c r="E102" s="1" t="s">
-        <v>13</v>
+        <v>24</v>
       </c>
       <c r="F102" s="2" t="s">
-        <v>10</v>
+        <v>2</v>
       </c>
       <c r="G102" s="1" t="s">
         <v>7</v>
@@ -1930,32 +1933,32 @@
       <c r="H102" s="4"/>
     </row>
     <row r="103" ht="36.0" customHeight="1">
-      <c r="D103" s="6" t="s">
+      <c r="D103" s="5" t="s">
+        <v>4</v>
+      </c>
+      <c r="E103" s="6" t="s">
+        <v>5</v>
+      </c>
+      <c r="F103" s="3" t="s">
+        <v>13</v>
+      </c>
+      <c r="G103" s="3" t="s">
+        <v>14</v>
+      </c>
+      <c r="H103" s="4"/>
+    </row>
+    <row r="104" ht="36.0" customHeight="1">
+      <c r="D104" s="7" t="s">
+        <v>15</v>
+      </c>
+      <c r="E104" s="1" t="s">
         <v>16</v>
       </c>
-      <c r="E103" s="1" t="s">
-        <v>17</v>
-      </c>
-      <c r="F103" s="3" t="s">
-        <v>18</v>
-      </c>
-      <c r="G103" s="3" t="s">
-        <v>19</v>
-      </c>
-      <c r="H103" s="4"/>
-    </row>
-    <row r="104" ht="36.0" customHeight="1">
-      <c r="D104" s="6" t="s">
-        <v>20</v>
-      </c>
-      <c r="E104" s="1" t="s">
-        <v>21</v>
-      </c>
-      <c r="F104" s="5" t="s">
-        <v>22</v>
-      </c>
-      <c r="G104" s="5" t="s">
-        <v>15</v>
+      <c r="F104" s="6" t="s">
+        <v>17</v>
+      </c>
+      <c r="G104" s="6" t="s">
+        <v>12</v>
       </c>
       <c r="H104" s="4"/>
     </row>
@@ -1966,11 +1969,11 @@
       <c r="E105" s="1" t="s">
         <v>9</v>
       </c>
-      <c r="F105" s="5" t="s">
-        <v>14</v>
+      <c r="F105" s="6" t="s">
+        <v>11</v>
       </c>
       <c r="G105" s="1" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="H105" s="4"/>
     </row>
@@ -1991,13 +1994,13 @@
     </row>
     <row r="107" ht="36.0" customHeight="1">
       <c r="D107" s="1" t="s">
-        <v>4</v>
+        <v>21</v>
       </c>
       <c r="E107" s="1" t="s">
-        <v>5</v>
+        <v>22</v>
       </c>
       <c r="F107" s="2" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="G107" s="1" t="s">
         <v>7</v>
@@ -2005,59 +2008,59 @@
       <c r="H107" s="4"/>
     </row>
     <row r="108" ht="36.0" customHeight="1">
-      <c r="D108" s="1" t="s">
-        <v>8</v>
-      </c>
-      <c r="E108" s="1" t="s">
-        <v>9</v>
-      </c>
-      <c r="F108" s="5" t="s">
-        <v>14</v>
+      <c r="D108" s="5" t="s">
+        <v>4</v>
+      </c>
+      <c r="E108" s="6" t="s">
+        <v>5</v>
+      </c>
+      <c r="F108" s="6" t="s">
+        <v>11</v>
       </c>
       <c r="G108" s="1" t="s">
+        <v>18</v>
+      </c>
+      <c r="H108" s="4"/>
+    </row>
+    <row r="109" ht="36.0" customHeight="1">
+      <c r="D109" s="7" t="s">
         <v>23</v>
       </c>
-      <c r="H108" s="4"/>
-    </row>
-    <row r="109" ht="36.0" customHeight="1">
-      <c r="D109" s="6" t="s">
-        <v>12</v>
-      </c>
       <c r="E109" s="1" t="s">
-        <v>13</v>
-      </c>
-      <c r="F109" s="5" t="s">
         <v>24</v>
       </c>
+      <c r="F109" s="6" t="s">
+        <v>17</v>
+      </c>
       <c r="G109" s="3" t="s">
-        <v>25</v>
+        <v>19</v>
       </c>
       <c r="H109" s="4"/>
     </row>
     <row r="110" ht="36.0" customHeight="1">
-      <c r="D110" s="6" t="s">
-        <v>16</v>
-      </c>
-      <c r="E110" s="1" t="s">
-        <v>17</v>
-      </c>
-      <c r="F110" s="5" t="s">
-        <v>28</v>
+      <c r="D110" s="5" t="s">
+        <v>4</v>
+      </c>
+      <c r="E110" s="6" t="s">
+        <v>5</v>
+      </c>
+      <c r="F110" s="6" t="s">
+        <v>27</v>
       </c>
       <c r="G110" s="1" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="H110" s="4"/>
     </row>
     <row r="111" ht="36.0" customHeight="1">
-      <c r="D111" s="6" t="s">
-        <v>20</v>
-      </c>
-      <c r="E111" s="1" t="s">
-        <v>21</v>
+      <c r="D111" s="5" t="s">
+        <v>4</v>
+      </c>
+      <c r="E111" s="6" t="s">
+        <v>5</v>
       </c>
       <c r="F111" s="2" t="s">
-        <v>10</v>
+        <v>2</v>
       </c>
       <c r="G111" s="1" t="s">
         <v>7</v>
@@ -2071,11 +2074,11 @@
       <c r="E112" s="1" t="s">
         <v>9</v>
       </c>
-      <c r="F112" s="5" t="s">
-        <v>28</v>
-      </c>
-      <c r="G112" s="5" t="s">
-        <v>15</v>
+      <c r="F112" s="6" t="s">
+        <v>27</v>
+      </c>
+      <c r="G112" s="6" t="s">
+        <v>12</v>
       </c>
       <c r="H112" s="4"/>
     </row>
@@ -2087,19 +2090,19 @@
         <v>1</v>
       </c>
       <c r="F113" s="3" t="s">
-        <v>18</v>
+        <v>13</v>
       </c>
       <c r="G113" s="3" t="s">
-        <v>19</v>
+        <v>14</v>
       </c>
       <c r="H113" s="4"/>
     </row>
     <row r="114" ht="36.0" customHeight="1">
       <c r="D114" s="1" t="s">
-        <v>4</v>
+        <v>21</v>
       </c>
       <c r="E114" s="1" t="s">
-        <v>5</v>
+        <v>22</v>
       </c>
       <c r="F114" s="2" t="s">
         <v>2</v>
@@ -2110,29 +2113,29 @@
       <c r="H114" s="4"/>
     </row>
     <row r="115" ht="36.0" customHeight="1">
-      <c r="D115" s="1" t="s">
-        <v>8</v>
-      </c>
-      <c r="E115" s="1" t="s">
-        <v>9</v>
-      </c>
-      <c r="F115" s="5" t="s">
-        <v>22</v>
+      <c r="D115" s="5" t="s">
+        <v>4</v>
+      </c>
+      <c r="E115" s="6" t="s">
+        <v>5</v>
+      </c>
+      <c r="F115" s="6" t="s">
+        <v>17</v>
       </c>
       <c r="G115" s="1" t="s">
+        <v>18</v>
+      </c>
+      <c r="H115" s="4"/>
+    </row>
+    <row r="116" ht="36.0" customHeight="1">
+      <c r="D116" s="7" t="s">
         <v>23</v>
       </c>
-      <c r="H115" s="4"/>
-    </row>
-    <row r="116" ht="36.0" customHeight="1">
-      <c r="D116" s="6" t="s">
-        <v>12</v>
-      </c>
       <c r="E116" s="1" t="s">
-        <v>13</v>
-      </c>
-      <c r="F116" s="5" t="s">
-        <v>22</v>
+        <v>24</v>
+      </c>
+      <c r="F116" s="6" t="s">
+        <v>17</v>
       </c>
       <c r="G116" s="1" t="s">
         <v>7</v>
@@ -2140,11 +2143,11 @@
       <c r="H116" s="4"/>
     </row>
     <row r="117" ht="36.0" customHeight="1">
-      <c r="D117" s="6" t="s">
-        <v>16</v>
-      </c>
-      <c r="E117" s="1" t="s">
-        <v>17</v>
+      <c r="D117" s="5" t="s">
+        <v>4</v>
+      </c>
+      <c r="E117" s="6" t="s">
+        <v>5</v>
       </c>
       <c r="F117" s="2" t="s">
         <v>2</v>
@@ -2155,17 +2158,17 @@
       <c r="H117" s="4"/>
     </row>
     <row r="118" ht="36.0" customHeight="1">
-      <c r="D118" s="6" t="s">
-        <v>20</v>
-      </c>
-      <c r="E118" s="1" t="s">
-        <v>21</v>
-      </c>
-      <c r="F118" s="5" t="s">
-        <v>22</v>
+      <c r="D118" s="5" t="s">
+        <v>4</v>
+      </c>
+      <c r="E118" s="6" t="s">
+        <v>5</v>
+      </c>
+      <c r="F118" s="6" t="s">
+        <v>17</v>
       </c>
       <c r="G118" s="1" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="H118" s="4"/>
     </row>
@@ -2177,10 +2180,10 @@
         <v>9</v>
       </c>
       <c r="F119" s="1" t="s">
-        <v>14</v>
-      </c>
-      <c r="G119" s="5" t="s">
-        <v>15</v>
+        <v>11</v>
+      </c>
+      <c r="G119" s="6" t="s">
+        <v>12</v>
       </c>
       <c r="H119" s="4"/>
     </row>
@@ -2192,7 +2195,7 @@
         <v>1</v>
       </c>
       <c r="F120" s="2" t="s">
-        <v>14</v>
+        <v>11</v>
       </c>
       <c r="G120" s="1" t="s">
         <v>7</v>
@@ -2201,10 +2204,10 @@
     </row>
     <row r="121" ht="36.0" customHeight="1">
       <c r="D121" s="1" t="s">
-        <v>4</v>
+        <v>21</v>
       </c>
       <c r="E121" s="1" t="s">
-        <v>5</v>
+        <v>22</v>
       </c>
       <c r="F121" s="2" t="s">
         <v>2</v>
@@ -2221,38 +2224,38 @@
       <c r="E122" s="1" t="s">
         <v>9</v>
       </c>
-      <c r="F122" s="5" t="s">
+      <c r="F122" s="6" t="s">
+        <v>11</v>
+      </c>
+      <c r="G122" s="1" t="s">
+        <v>10</v>
+      </c>
+      <c r="H122" s="4"/>
+    </row>
+    <row r="123" ht="36.0" customHeight="1">
+      <c r="D123" s="5" t="s">
+        <v>4</v>
+      </c>
+      <c r="E123" s="6" t="s">
+        <v>5</v>
+      </c>
+      <c r="F123" s="3" t="s">
+        <v>13</v>
+      </c>
+      <c r="G123" s="3" t="s">
         <v>14</v>
       </c>
-      <c r="G122" s="1" t="s">
-        <v>11</v>
-      </c>
-      <c r="H122" s="4"/>
-    </row>
-    <row r="123" ht="36.0" customHeight="1">
-      <c r="D123" s="6" t="s">
-        <v>12</v>
-      </c>
-      <c r="E123" s="1" t="s">
-        <v>13</v>
-      </c>
-      <c r="F123" s="3" t="s">
-        <v>18</v>
-      </c>
-      <c r="G123" s="3" t="s">
-        <v>19</v>
-      </c>
       <c r="H123" s="4"/>
     </row>
     <row r="124" ht="36.0" customHeight="1">
-      <c r="D124" s="6" t="s">
-        <v>16</v>
-      </c>
-      <c r="E124" s="1" t="s">
-        <v>17</v>
+      <c r="D124" s="5" t="s">
+        <v>4</v>
+      </c>
+      <c r="E124" s="6" t="s">
+        <v>5</v>
       </c>
       <c r="F124" s="2" t="s">
-        <v>2</v>
+        <v>20</v>
       </c>
       <c r="G124" s="1" t="s">
         <v>7</v>
@@ -2260,17 +2263,17 @@
       <c r="H124" s="4"/>
     </row>
     <row r="125" ht="36.0" customHeight="1">
-      <c r="D125" s="6" t="s">
-        <v>20</v>
-      </c>
-      <c r="E125" s="1" t="s">
-        <v>21</v>
+      <c r="D125" s="5" t="s">
+        <v>4</v>
+      </c>
+      <c r="E125" s="6" t="s">
+        <v>5</v>
       </c>
       <c r="F125" s="1" t="s">
-        <v>14</v>
-      </c>
-      <c r="G125" s="5" t="s">
-        <v>15</v>
+        <v>11</v>
+      </c>
+      <c r="G125" s="6" t="s">
+        <v>12</v>
       </c>
       <c r="H125" s="4"/>
     </row>
@@ -2296,7 +2299,7 @@
       <c r="E127" s="1" t="s">
         <v>1</v>
       </c>
-      <c r="F127" s="5" t="s">
+      <c r="F127" s="6" t="s">
         <v>6</v>
       </c>
       <c r="G127" s="1" t="s">
@@ -2306,16 +2309,16 @@
     </row>
     <row r="128" ht="36.0" customHeight="1">
       <c r="D128" s="1" t="s">
-        <v>4</v>
+        <v>21</v>
       </c>
       <c r="E128" s="1" t="s">
-        <v>5</v>
-      </c>
-      <c r="F128" s="5" t="s">
-        <v>24</v>
+        <v>22</v>
+      </c>
+      <c r="F128" s="6" t="s">
+        <v>17</v>
       </c>
       <c r="G128" s="3" t="s">
-        <v>25</v>
+        <v>19</v>
       </c>
       <c r="H128" s="4"/>
     </row>
@@ -2335,47 +2338,47 @@
       <c r="H129" s="4"/>
     </row>
     <row r="130" ht="36.0" customHeight="1">
-      <c r="D130" s="6" t="s">
+      <c r="D130" s="7" t="s">
+        <v>23</v>
+      </c>
+      <c r="E130" s="1" t="s">
+        <v>24</v>
+      </c>
+      <c r="F130" s="6" t="s">
+        <v>6</v>
+      </c>
+      <c r="G130" s="6" t="s">
         <v>12</v>
       </c>
-      <c r="E130" s="1" t="s">
+      <c r="H130" s="4"/>
+    </row>
+    <row r="131" ht="36.0" customHeight="1">
+      <c r="D131" s="5" t="s">
+        <v>4</v>
+      </c>
+      <c r="E131" s="6" t="s">
+        <v>5</v>
+      </c>
+      <c r="F131" s="3" t="s">
         <v>13</v>
       </c>
-      <c r="F130" s="5" t="s">
-        <v>6</v>
-      </c>
-      <c r="G130" s="5" t="s">
-        <v>15</v>
-      </c>
-      <c r="H130" s="4"/>
-    </row>
-    <row r="131" ht="36.0" customHeight="1">
-      <c r="D131" s="6" t="s">
-        <v>16</v>
-      </c>
-      <c r="E131" s="1" t="s">
-        <v>17</v>
-      </c>
-      <c r="F131" s="3" t="s">
-        <v>18</v>
-      </c>
       <c r="G131" s="3" t="s">
-        <v>19</v>
+        <v>14</v>
       </c>
       <c r="H131" s="4"/>
     </row>
     <row r="132" ht="36.0" customHeight="1">
-      <c r="D132" s="6" t="s">
-        <v>20</v>
-      </c>
-      <c r="E132" s="1" t="s">
-        <v>21</v>
-      </c>
-      <c r="F132" s="5" t="s">
-        <v>10</v>
+      <c r="D132" s="5" t="s">
+        <v>4</v>
+      </c>
+      <c r="E132" s="6" t="s">
+        <v>5</v>
+      </c>
+      <c r="F132" s="6" t="s">
+        <v>2</v>
       </c>
       <c r="G132" s="1" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="H132" s="4"/>
     </row>
@@ -2401,20 +2404,20 @@
       <c r="E134" s="1" t="s">
         <v>1</v>
       </c>
-      <c r="F134" s="5" t="s">
-        <v>24</v>
+      <c r="F134" s="6" t="s">
+        <v>17</v>
       </c>
       <c r="G134" s="3" t="s">
-        <v>25</v>
+        <v>19</v>
       </c>
       <c r="H134" s="4"/>
     </row>
     <row r="135" ht="36.0" customHeight="1">
       <c r="D135" s="1" t="s">
-        <v>4</v>
+        <v>21</v>
       </c>
       <c r="E135" s="1" t="s">
-        <v>5</v>
+        <v>22</v>
       </c>
       <c r="F135" s="2" t="s">
         <v>2</v>
@@ -2425,77 +2428,77 @@
       <c r="H135" s="4"/>
     </row>
     <row r="136" ht="36.0" customHeight="1">
-      <c r="D136" s="1" t="s">
-        <v>8</v>
-      </c>
-      <c r="E136" s="1" t="s">
-        <v>9</v>
+      <c r="D136" s="5" t="s">
+        <v>4</v>
+      </c>
+      <c r="E136" s="6" t="s">
+        <v>5</v>
       </c>
       <c r="F136" s="2" t="s">
-        <v>2</v>
+        <v>20</v>
       </c>
       <c r="G136" s="3" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="H136" s="3"/>
     </row>
     <row r="137" ht="36.0" customHeight="1">
-      <c r="D137" s="6" t="s">
+      <c r="D137" s="7" t="s">
+        <v>23</v>
+      </c>
+      <c r="E137" s="1" t="s">
+        <v>24</v>
+      </c>
+      <c r="F137" s="6" t="s">
+        <v>27</v>
+      </c>
+      <c r="G137" s="1" t="s">
+        <v>10</v>
+      </c>
+      <c r="H137" s="4"/>
+    </row>
+    <row r="138" ht="36.0" customHeight="1">
+      <c r="D138" s="5" t="s">
+        <v>4</v>
+      </c>
+      <c r="E138" s="6" t="s">
+        <v>5</v>
+      </c>
+      <c r="F138" s="2" t="s">
+        <v>2</v>
+      </c>
+      <c r="G138" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="H138" s="4"/>
+    </row>
+    <row r="139" ht="36.0" customHeight="1">
+      <c r="D139" s="5" t="s">
+        <v>4</v>
+      </c>
+      <c r="E139" s="6" t="s">
+        <v>5</v>
+      </c>
+      <c r="F139" s="6" t="s">
+        <v>11</v>
+      </c>
+      <c r="G139" s="1" t="s">
+        <v>18</v>
+      </c>
+      <c r="H139" s="4"/>
+    </row>
+    <row r="140" ht="36.0" customHeight="1">
+      <c r="D140" s="5" t="s">
+        <v>4</v>
+      </c>
+      <c r="E140" s="6" t="s">
+        <v>5</v>
+      </c>
+      <c r="F140" s="1" t="s">
+        <v>11</v>
+      </c>
+      <c r="G140" s="6" t="s">
         <v>12</v>
-      </c>
-      <c r="E137" s="1" t="s">
-        <v>13</v>
-      </c>
-      <c r="F137" s="5" t="s">
-        <v>28</v>
-      </c>
-      <c r="G137" s="1" t="s">
-        <v>11</v>
-      </c>
-      <c r="H137" s="4"/>
-    </row>
-    <row r="138" ht="36.0" customHeight="1">
-      <c r="D138" s="6" t="s">
-        <v>16</v>
-      </c>
-      <c r="E138" s="1" t="s">
-        <v>17</v>
-      </c>
-      <c r="F138" s="2" t="s">
-        <v>2</v>
-      </c>
-      <c r="G138" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="H138" s="4"/>
-    </row>
-    <row r="139" ht="36.0" customHeight="1">
-      <c r="D139" s="6" t="s">
-        <v>20</v>
-      </c>
-      <c r="E139" s="1" t="s">
-        <v>21</v>
-      </c>
-      <c r="F139" s="5" t="s">
-        <v>14</v>
-      </c>
-      <c r="G139" s="1" t="s">
-        <v>23</v>
-      </c>
-      <c r="H139" s="4"/>
-    </row>
-    <row r="140" ht="36.0" customHeight="1">
-      <c r="D140" s="1" t="s">
-        <v>8</v>
-      </c>
-      <c r="E140" s="1" t="s">
-        <v>9</v>
-      </c>
-      <c r="F140" s="1" t="s">
-        <v>14</v>
-      </c>
-      <c r="G140" s="5" t="s">
-        <v>15</v>
       </c>
       <c r="H140" s="4"/>
     </row>
@@ -2506,20 +2509,20 @@
       <c r="E141" s="1" t="s">
         <v>1</v>
       </c>
-      <c r="F141" s="5" t="s">
-        <v>22</v>
+      <c r="F141" s="6" t="s">
+        <v>17</v>
       </c>
       <c r="G141" s="1" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="H141" s="4"/>
     </row>
     <row r="142" ht="36.0" customHeight="1">
       <c r="D142" s="1" t="s">
-        <v>4</v>
+        <v>21</v>
       </c>
       <c r="E142" s="1" t="s">
-        <v>5</v>
+        <v>22</v>
       </c>
       <c r="F142" s="2" t="s">
         <v>2</v>
@@ -2536,7 +2539,7 @@
       <c r="E143" s="1" t="s">
         <v>9</v>
       </c>
-      <c r="F143" s="5" t="s">
+      <c r="F143" s="6" t="s">
         <v>6</v>
       </c>
       <c r="G143" s="1" t="s">
@@ -2545,47 +2548,47 @@
       <c r="H143" s="4"/>
     </row>
     <row r="144" ht="36.0" customHeight="1">
-      <c r="D144" s="6" t="s">
-        <v>12</v>
+      <c r="D144" s="7" t="s">
+        <v>23</v>
       </c>
       <c r="E144" s="1" t="s">
-        <v>13</v>
-      </c>
-      <c r="F144" s="5" t="s">
-        <v>14</v>
+        <v>24</v>
+      </c>
+      <c r="F144" s="6" t="s">
+        <v>11</v>
       </c>
       <c r="G144" s="1" t="s">
-        <v>23</v>
+        <v>18</v>
       </c>
       <c r="H144" s="4"/>
     </row>
     <row r="145" ht="36.0" customHeight="1">
-      <c r="D145" s="6" t="s">
-        <v>16</v>
-      </c>
-      <c r="E145" s="1" t="s">
-        <v>17</v>
-      </c>
-      <c r="F145" s="5" t="s">
-        <v>22</v>
+      <c r="D145" s="5" t="s">
+        <v>4</v>
+      </c>
+      <c r="E145" s="6" t="s">
+        <v>5</v>
+      </c>
+      <c r="F145" s="6" t="s">
+        <v>17</v>
       </c>
       <c r="G145" s="1" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="H145" s="4"/>
     </row>
     <row r="146" ht="36.0" customHeight="1">
-      <c r="D146" s="6" t="s">
-        <v>20</v>
-      </c>
-      <c r="E146" s="1" t="s">
-        <v>21</v>
-      </c>
-      <c r="F146" s="5" t="s">
-        <v>22</v>
+      <c r="D146" s="5" t="s">
+        <v>4</v>
+      </c>
+      <c r="E146" s="6" t="s">
+        <v>5</v>
+      </c>
+      <c r="F146" s="6" t="s">
+        <v>17</v>
       </c>
       <c r="G146" s="1" t="s">
-        <v>23</v>
+        <v>18</v>
       </c>
       <c r="H146" s="4"/>
     </row>
@@ -2605,32 +2608,32 @@
       <c r="H147" s="4"/>
     </row>
     <row r="148" ht="36.0" customHeight="1">
-      <c r="D148" s="1" t="s">
-        <v>0</v>
-      </c>
-      <c r="E148" s="1" t="s">
-        <v>1</v>
+      <c r="D148" s="5" t="s">
+        <v>4</v>
+      </c>
+      <c r="E148" s="6" t="s">
+        <v>5</v>
       </c>
       <c r="F148" s="3" t="s">
-        <v>18</v>
+        <v>13</v>
       </c>
       <c r="G148" s="3" t="s">
-        <v>19</v>
+        <v>14</v>
       </c>
       <c r="H148" s="4"/>
     </row>
     <row r="149" ht="36.0" customHeight="1">
       <c r="D149" s="1" t="s">
-        <v>4</v>
+        <v>21</v>
       </c>
       <c r="E149" s="1" t="s">
-        <v>5</v>
-      </c>
-      <c r="F149" s="5" t="s">
-        <v>24</v>
+        <v>22</v>
+      </c>
+      <c r="F149" s="6" t="s">
+        <v>17</v>
       </c>
       <c r="G149" s="3" t="s">
-        <v>25</v>
+        <v>19</v>
       </c>
       <c r="H149" s="4"/>
     </row>
@@ -2641,53 +2644,53 @@
       <c r="E150" s="1" t="s">
         <v>9</v>
       </c>
-      <c r="F150" s="5" t="s">
-        <v>14</v>
+      <c r="F150" s="6" t="s">
+        <v>11</v>
       </c>
       <c r="G150" s="1" t="s">
+        <v>18</v>
+      </c>
+      <c r="H150" s="4"/>
+    </row>
+    <row r="151" ht="36.0" customHeight="1">
+      <c r="D151" s="7" t="s">
         <v>23</v>
       </c>
-      <c r="H150" s="4"/>
-    </row>
-    <row r="151" ht="36.0" customHeight="1">
-      <c r="D151" s="6" t="s">
+      <c r="E151" s="1" t="s">
+        <v>24</v>
+      </c>
+      <c r="F151" s="2" t="s">
+        <v>2</v>
+      </c>
+      <c r="G151" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="H151" s="4"/>
+    </row>
+    <row r="152" ht="36.0" customHeight="1">
+      <c r="D152" s="5" t="s">
+        <v>4</v>
+      </c>
+      <c r="E152" s="6" t="s">
+        <v>5</v>
+      </c>
+      <c r="F152" s="1" t="s">
+        <v>11</v>
+      </c>
+      <c r="G152" s="6" t="s">
         <v>12</v>
       </c>
-      <c r="E151" s="1" t="s">
-        <v>13</v>
-      </c>
-      <c r="F151" s="2" t="s">
-        <v>2</v>
-      </c>
-      <c r="G151" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="H151" s="4"/>
-    </row>
-    <row r="152" ht="36.0" customHeight="1">
-      <c r="D152" s="6" t="s">
-        <v>16</v>
-      </c>
-      <c r="E152" s="1" t="s">
-        <v>17</v>
-      </c>
-      <c r="F152" s="1" t="s">
-        <v>14</v>
-      </c>
-      <c r="G152" s="5" t="s">
-        <v>15</v>
-      </c>
       <c r="H152" s="4"/>
     </row>
     <row r="153" ht="36.0" customHeight="1">
-      <c r="D153" s="6" t="s">
-        <v>20</v>
-      </c>
-      <c r="E153" s="1" t="s">
-        <v>21</v>
-      </c>
-      <c r="F153" s="5" t="s">
-        <v>27</v>
+      <c r="D153" s="5" t="s">
+        <v>4</v>
+      </c>
+      <c r="E153" s="6" t="s">
+        <v>5</v>
+      </c>
+      <c r="F153" s="6" t="s">
+        <v>26</v>
       </c>
       <c r="G153" s="1" t="s">
         <v>7</v>
@@ -2695,17 +2698,17 @@
       <c r="H153" s="4"/>
     </row>
     <row r="154" ht="36.0" customHeight="1">
-      <c r="D154" s="1" t="s">
-        <v>8</v>
-      </c>
-      <c r="E154" s="1" t="s">
-        <v>9</v>
-      </c>
-      <c r="F154" s="5" t="s">
-        <v>10</v>
+      <c r="D154" s="5" t="s">
+        <v>4</v>
+      </c>
+      <c r="E154" s="6" t="s">
+        <v>5</v>
+      </c>
+      <c r="F154" s="6" t="s">
+        <v>2</v>
       </c>
       <c r="G154" s="1" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="H154" s="4"/>
     </row>
@@ -2716,20 +2719,20 @@
       <c r="E155" s="1" t="s">
         <v>1</v>
       </c>
-      <c r="F155" s="5" t="s">
-        <v>24</v>
+      <c r="F155" s="6" t="s">
+        <v>17</v>
       </c>
       <c r="G155" s="3" t="s">
-        <v>25</v>
+        <v>19</v>
       </c>
       <c r="H155" s="4"/>
     </row>
     <row r="156" ht="36.0" customHeight="1">
       <c r="D156" s="1" t="s">
-        <v>4</v>
+        <v>21</v>
       </c>
       <c r="E156" s="1" t="s">
-        <v>5</v>
+        <v>22</v>
       </c>
       <c r="F156" s="2" t="s">
         <v>2</v>
@@ -2746,38 +2749,38 @@
       <c r="E157" s="1" t="s">
         <v>9</v>
       </c>
-      <c r="F157" s="5" t="s">
+      <c r="F157" s="6" t="s">
+        <v>11</v>
+      </c>
+      <c r="G157" s="1" t="s">
+        <v>10</v>
+      </c>
+      <c r="H157" s="4"/>
+    </row>
+    <row r="158" ht="36.0" customHeight="1">
+      <c r="D158" s="7" t="s">
+        <v>23</v>
+      </c>
+      <c r="E158" s="1" t="s">
+        <v>24</v>
+      </c>
+      <c r="F158" s="6" t="s">
+        <v>11</v>
+      </c>
+      <c r="G158" s="3" t="s">
         <v>14</v>
       </c>
-      <c r="G157" s="1" t="s">
-        <v>11</v>
-      </c>
-      <c r="H157" s="4"/>
-    </row>
-    <row r="158" ht="36.0" customHeight="1">
-      <c r="D158" s="6" t="s">
-        <v>12</v>
-      </c>
-      <c r="E158" s="1" t="s">
-        <v>13</v>
-      </c>
-      <c r="F158" s="5" t="s">
-        <v>14</v>
-      </c>
-      <c r="G158" s="3" t="s">
-        <v>19</v>
-      </c>
       <c r="H158" s="4"/>
     </row>
     <row r="159" ht="36.0" customHeight="1">
-      <c r="D159" s="6" t="s">
-        <v>16</v>
-      </c>
-      <c r="E159" s="1" t="s">
-        <v>17</v>
-      </c>
-      <c r="F159" s="5" t="s">
-        <v>14</v>
+      <c r="D159" s="5" t="s">
+        <v>4</v>
+      </c>
+      <c r="E159" s="6" t="s">
+        <v>5</v>
+      </c>
+      <c r="F159" s="6" t="s">
+        <v>11</v>
       </c>
       <c r="G159" s="1" t="s">
         <v>7</v>
@@ -2785,11 +2788,11 @@
       <c r="H159" s="4"/>
     </row>
     <row r="160" ht="36.0" customHeight="1">
-      <c r="D160" s="6" t="s">
-        <v>20</v>
-      </c>
-      <c r="E160" s="1" t="s">
-        <v>21</v>
+      <c r="D160" s="5" t="s">
+        <v>4</v>
+      </c>
+      <c r="E160" s="6" t="s">
+        <v>5</v>
       </c>
       <c r="F160" s="2" t="s">
         <v>2</v>
@@ -2806,11 +2809,11 @@
       <c r="E161" s="1" t="s">
         <v>9</v>
       </c>
-      <c r="F161" s="5" t="s">
-        <v>22</v>
+      <c r="F161" s="6" t="s">
+        <v>17</v>
       </c>
       <c r="G161" s="1" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="H161" s="4"/>
     </row>
@@ -2821,26 +2824,26 @@
       <c r="E162" s="1" t="s">
         <v>1</v>
       </c>
-      <c r="F162" s="5" t="s">
+      <c r="F162" s="6" t="s">
+        <v>11</v>
+      </c>
+      <c r="G162" s="3" t="s">
         <v>14</v>
-      </c>
-      <c r="G162" s="3" t="s">
-        <v>19</v>
       </c>
       <c r="H162" s="4"/>
     </row>
     <row r="163" ht="36.0" customHeight="1">
       <c r="D163" s="1" t="s">
-        <v>4</v>
+        <v>21</v>
       </c>
       <c r="E163" s="1" t="s">
-        <v>5</v>
-      </c>
-      <c r="F163" s="5" t="s">
         <v>22</v>
       </c>
+      <c r="F163" s="6" t="s">
+        <v>17</v>
+      </c>
       <c r="G163" s="1" t="s">
-        <v>23</v>
+        <v>18</v>
       </c>
       <c r="H163" s="4"/>
     </row>
@@ -2852,7 +2855,7 @@
         <v>9</v>
       </c>
       <c r="F164" s="2" t="s">
-        <v>2</v>
+        <v>20</v>
       </c>
       <c r="G164" s="1" t="s">
         <v>7</v>
@@ -2860,47 +2863,47 @@
       <c r="H164" s="4"/>
     </row>
     <row r="165" ht="36.0" customHeight="1">
-      <c r="D165" s="6" t="s">
-        <v>12</v>
-      </c>
-      <c r="E165" s="1" t="s">
-        <v>13</v>
-      </c>
-      <c r="F165" s="5" t="s">
+      <c r="D165" s="5" t="s">
+        <v>4</v>
+      </c>
+      <c r="E165" s="6" t="s">
+        <v>5</v>
+      </c>
+      <c r="F165" s="6" t="s">
+        <v>11</v>
+      </c>
+      <c r="G165" s="1" t="s">
+        <v>10</v>
+      </c>
+      <c r="H165" s="4"/>
+    </row>
+    <row r="166" ht="36.0" customHeight="1">
+      <c r="D166" s="5" t="s">
+        <v>4</v>
+      </c>
+      <c r="E166" s="6" t="s">
+        <v>5</v>
+      </c>
+      <c r="F166" s="2" t="s">
+        <v>2</v>
+      </c>
+      <c r="G166" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="H166" s="4"/>
+    </row>
+    <row r="167" ht="36.0" customHeight="1">
+      <c r="D167" s="5" t="s">
+        <v>4</v>
+      </c>
+      <c r="E167" s="6" t="s">
+        <v>5</v>
+      </c>
+      <c r="F167" s="6" t="s">
+        <v>11</v>
+      </c>
+      <c r="G167" s="3" t="s">
         <v>14</v>
-      </c>
-      <c r="G165" s="1" t="s">
-        <v>11</v>
-      </c>
-      <c r="H165" s="4"/>
-    </row>
-    <row r="166" ht="36.0" customHeight="1">
-      <c r="D166" s="6" t="s">
-        <v>16</v>
-      </c>
-      <c r="E166" s="1" t="s">
-        <v>17</v>
-      </c>
-      <c r="F166" s="2" t="s">
-        <v>2</v>
-      </c>
-      <c r="G166" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="H166" s="4"/>
-    </row>
-    <row r="167" ht="36.0" customHeight="1">
-      <c r="D167" s="6" t="s">
-        <v>20</v>
-      </c>
-      <c r="E167" s="1" t="s">
-        <v>21</v>
-      </c>
-      <c r="F167" s="5" t="s">
-        <v>14</v>
-      </c>
-      <c r="G167" s="3" t="s">
-        <v>19</v>
       </c>
       <c r="H167" s="4"/>
     </row>
@@ -2911,11 +2914,11 @@
       <c r="E168" s="1" t="s">
         <v>9</v>
       </c>
-      <c r="F168" s="5" t="s">
-        <v>14</v>
+      <c r="F168" s="6" t="s">
+        <v>11</v>
       </c>
       <c r="G168" s="1" t="s">
-        <v>23</v>
+        <v>18</v>
       </c>
       <c r="H168" s="4"/>
     </row>
@@ -2926,35 +2929,35 @@
       <c r="E169" s="1" t="s">
         <v>1</v>
       </c>
-      <c r="F169" s="5" t="s">
-        <v>24</v>
+      <c r="F169" s="6" t="s">
+        <v>17</v>
       </c>
       <c r="G169" s="3" t="s">
-        <v>25</v>
+        <v>19</v>
       </c>
       <c r="H169" s="4"/>
     </row>
     <row r="170" ht="36.0" customHeight="1">
       <c r="D170" s="1" t="s">
-        <v>4</v>
+        <v>21</v>
       </c>
       <c r="E170" s="1" t="s">
-        <v>5</v>
-      </c>
-      <c r="F170" s="5" t="s">
-        <v>14</v>
+        <v>22</v>
+      </c>
+      <c r="F170" s="6" t="s">
+        <v>11</v>
       </c>
       <c r="G170" s="1" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="H170" s="4"/>
     </row>
     <row r="171" ht="36.0" customHeight="1">
-      <c r="D171" s="1" t="s">
-        <v>8</v>
-      </c>
-      <c r="E171" s="1" t="s">
-        <v>9</v>
+      <c r="D171" s="5" t="s">
+        <v>4</v>
+      </c>
+      <c r="E171" s="6" t="s">
+        <v>5</v>
       </c>
       <c r="F171" s="2" t="s">
         <v>2</v>
@@ -2965,26 +2968,26 @@
       <c r="H171" s="4"/>
     </row>
     <row r="172" ht="36.0" customHeight="1">
-      <c r="D172" s="6" t="s">
-        <v>12</v>
+      <c r="D172" s="7" t="s">
+        <v>23</v>
       </c>
       <c r="E172" s="1" t="s">
-        <v>13</v>
-      </c>
-      <c r="F172" s="5" t="s">
-        <v>10</v>
+        <v>24</v>
+      </c>
+      <c r="F172" s="6" t="s">
+        <v>2</v>
       </c>
       <c r="G172" s="1" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="H172" s="4"/>
     </row>
     <row r="173" ht="36.0" customHeight="1">
-      <c r="D173" s="6" t="s">
-        <v>16</v>
-      </c>
-      <c r="E173" s="1" t="s">
-        <v>17</v>
+      <c r="D173" s="5" t="s">
+        <v>4</v>
+      </c>
+      <c r="E173" s="6" t="s">
+        <v>5</v>
       </c>
       <c r="F173" s="2" t="s">
         <v>2</v>
@@ -2995,14 +2998,14 @@
       <c r="H173" s="4"/>
     </row>
     <row r="174" ht="36.0" customHeight="1">
-      <c r="D174" s="6" t="s">
-        <v>20</v>
-      </c>
-      <c r="E174" s="1" t="s">
-        <v>21</v>
+      <c r="D174" s="5" t="s">
+        <v>4</v>
+      </c>
+      <c r="E174" s="6" t="s">
+        <v>5</v>
       </c>
       <c r="F174" s="2" t="s">
-        <v>22</v>
+        <v>17</v>
       </c>
       <c r="G174" s="1" t="s">
         <v>7</v>
@@ -3016,11 +3019,11 @@
       <c r="E175" s="1" t="s">
         <v>9</v>
       </c>
-      <c r="F175" s="5" t="s">
-        <v>24</v>
+      <c r="F175" s="6" t="s">
+        <v>28</v>
       </c>
       <c r="G175" s="3" t="s">
-        <v>25</v>
+        <v>19</v>
       </c>
       <c r="H175" s="4"/>
     </row>
@@ -3041,28 +3044,28 @@
     </row>
     <row r="177" ht="36.0" customHeight="1">
       <c r="D177" s="1" t="s">
-        <v>4</v>
+        <v>21</v>
       </c>
       <c r="E177" s="1" t="s">
-        <v>5</v>
-      </c>
-      <c r="F177" s="5" t="s">
-        <v>14</v>
+        <v>22</v>
+      </c>
+      <c r="F177" s="6" t="s">
+        <v>11</v>
       </c>
       <c r="G177" s="1" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="H177" s="4"/>
     </row>
     <row r="178" ht="36.0" customHeight="1">
-      <c r="D178" s="1" t="s">
-        <v>8</v>
-      </c>
-      <c r="E178" s="1" t="s">
-        <v>9</v>
+      <c r="D178" s="5" t="s">
+        <v>4</v>
+      </c>
+      <c r="E178" s="6" t="s">
+        <v>5</v>
       </c>
       <c r="F178" s="2" t="s">
-        <v>14</v>
+        <v>11</v>
       </c>
       <c r="G178" s="1" t="s">
         <v>7</v>
@@ -3070,26 +3073,26 @@
       <c r="H178" s="4"/>
     </row>
     <row r="179" ht="36.0" customHeight="1">
-      <c r="D179" s="6" t="s">
-        <v>12</v>
+      <c r="D179" s="7" t="s">
+        <v>23</v>
       </c>
       <c r="E179" s="1" t="s">
-        <v>13</v>
+        <v>24</v>
       </c>
       <c r="F179" s="2" t="s">
-        <v>10</v>
+        <v>2</v>
       </c>
       <c r="G179" s="3" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="H179" s="3"/>
     </row>
     <row r="180" ht="36.0" customHeight="1">
-      <c r="D180" s="6" t="s">
-        <v>16</v>
-      </c>
-      <c r="E180" s="1" t="s">
-        <v>17</v>
+      <c r="D180" s="5" t="s">
+        <v>4</v>
+      </c>
+      <c r="E180" s="6" t="s">
+        <v>5</v>
       </c>
       <c r="F180" s="2" t="s">
         <v>2</v>
@@ -3100,17 +3103,17 @@
       <c r="H180" s="4"/>
     </row>
     <row r="181" ht="36.0" customHeight="1">
-      <c r="D181" s="6" t="s">
-        <v>20</v>
-      </c>
-      <c r="E181" s="1" t="s">
-        <v>21</v>
-      </c>
-      <c r="F181" s="5" t="s">
-        <v>24</v>
+      <c r="D181" s="5" t="s">
+        <v>4</v>
+      </c>
+      <c r="E181" s="6" t="s">
+        <v>5</v>
+      </c>
+      <c r="F181" s="6" t="s">
+        <v>17</v>
       </c>
       <c r="G181" s="3" t="s">
-        <v>25</v>
+        <v>19</v>
       </c>
       <c r="H181" s="4"/>
     </row>
@@ -3121,11 +3124,11 @@
       <c r="E182" s="1" t="s">
         <v>9</v>
       </c>
-      <c r="F182" s="5" t="s">
-        <v>22</v>
+      <c r="F182" s="6" t="s">
+        <v>17</v>
       </c>
       <c r="G182" s="1" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="H182" s="4"/>
     </row>
@@ -3137,7 +3140,7 @@
         <v>1</v>
       </c>
       <c r="F183" s="2" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="G183" s="1" t="s">
         <v>7</v>
@@ -3146,10 +3149,10 @@
     </row>
     <row r="184" ht="36.0" customHeight="1">
       <c r="D184" s="1" t="s">
-        <v>4</v>
+        <v>21</v>
       </c>
       <c r="E184" s="1" t="s">
-        <v>5</v>
+        <v>22</v>
       </c>
       <c r="F184" s="2" t="s">
         <v>2</v>
@@ -3166,37 +3169,37 @@
       <c r="E185" s="1" t="s">
         <v>9</v>
       </c>
-      <c r="F185" s="5" t="s">
+      <c r="F185" s="6" t="s">
+        <v>11</v>
+      </c>
+      <c r="G185" s="1" t="s">
+        <v>10</v>
+      </c>
+      <c r="H185" s="4"/>
+    </row>
+    <row r="186" ht="36.0" customHeight="1">
+      <c r="D186" s="7" t="s">
+        <v>23</v>
+      </c>
+      <c r="E186" s="1" t="s">
+        <v>24</v>
+      </c>
+      <c r="F186" s="6" t="s">
+        <v>11</v>
+      </c>
+      <c r="G186" s="3" t="s">
         <v>14</v>
       </c>
-      <c r="G185" s="1" t="s">
-        <v>11</v>
-      </c>
-      <c r="H185" s="4"/>
-    </row>
-    <row r="186" ht="36.0" customHeight="1">
-      <c r="D186" s="6" t="s">
-        <v>12</v>
-      </c>
-      <c r="E186" s="1" t="s">
-        <v>13</v>
-      </c>
-      <c r="F186" s="5" t="s">
-        <v>14</v>
-      </c>
-      <c r="G186" s="3" t="s">
-        <v>19</v>
-      </c>
       <c r="H186" s="4"/>
     </row>
     <row r="187" ht="36.0" customHeight="1">
-      <c r="D187" s="6" t="s">
-        <v>16</v>
-      </c>
-      <c r="E187" s="1" t="s">
-        <v>17</v>
-      </c>
-      <c r="F187" s="5" t="s">
+      <c r="D187" s="5" t="s">
+        <v>4</v>
+      </c>
+      <c r="E187" s="6" t="s">
+        <v>5</v>
+      </c>
+      <c r="F187" s="6" t="s">
         <v>6</v>
       </c>
       <c r="G187" s="1" t="s">
@@ -3205,11 +3208,11 @@
       <c r="H187" s="4"/>
     </row>
     <row r="188" ht="36.0" customHeight="1">
-      <c r="D188" s="6" t="s">
-        <v>20</v>
-      </c>
-      <c r="E188" s="1" t="s">
-        <v>21</v>
+      <c r="D188" s="5" t="s">
+        <v>4</v>
+      </c>
+      <c r="E188" s="6" t="s">
+        <v>5</v>
       </c>
       <c r="F188" s="2" t="s">
         <v>2</v>
@@ -3226,11 +3229,11 @@
       <c r="E189" s="1" t="s">
         <v>9</v>
       </c>
-      <c r="F189" s="5" t="s">
-        <v>27</v>
+      <c r="F189" s="6" t="s">
+        <v>26</v>
       </c>
       <c r="G189" s="1" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="H189" s="4"/>
     </row>
@@ -3241,23 +3244,23 @@
       <c r="E190" s="1" t="s">
         <v>1</v>
       </c>
-      <c r="F190" s="5" t="s">
-        <v>14</v>
+      <c r="F190" s="6" t="s">
+        <v>11</v>
       </c>
       <c r="G190" s="1" t="s">
-        <v>23</v>
+        <v>18</v>
       </c>
       <c r="H190" s="4"/>
     </row>
     <row r="191" ht="36.0" customHeight="1">
       <c r="D191" s="1" t="s">
-        <v>4</v>
+        <v>21</v>
       </c>
       <c r="E191" s="1" t="s">
-        <v>5</v>
-      </c>
-      <c r="F191" s="5" t="s">
-        <v>27</v>
+        <v>22</v>
+      </c>
+      <c r="F191" s="6" t="s">
+        <v>26</v>
       </c>
       <c r="G191" s="1" t="s">
         <v>7</v>
@@ -3271,35 +3274,35 @@
       <c r="E192" s="1" t="s">
         <v>9</v>
       </c>
-      <c r="F192" s="5" t="s">
-        <v>24</v>
+      <c r="F192" s="6" t="s">
+        <v>17</v>
       </c>
       <c r="G192" s="3" t="s">
-        <v>25</v>
+        <v>19</v>
       </c>
       <c r="H192" s="4"/>
     </row>
     <row r="193" ht="36.0" customHeight="1">
-      <c r="D193" s="6" t="s">
-        <v>12</v>
-      </c>
-      <c r="E193" s="1" t="s">
-        <v>13</v>
-      </c>
-      <c r="F193" s="5" t="s">
+      <c r="D193" s="5" t="s">
+        <v>4</v>
+      </c>
+      <c r="E193" s="6" t="s">
+        <v>5</v>
+      </c>
+      <c r="F193" s="6" t="s">
+        <v>11</v>
+      </c>
+      <c r="G193" s="3" t="s">
         <v>14</v>
       </c>
-      <c r="G193" s="3" t="s">
-        <v>19</v>
-      </c>
       <c r="H193" s="4"/>
     </row>
     <row r="194" ht="36.0" customHeight="1">
-      <c r="D194" s="6" t="s">
-        <v>16</v>
-      </c>
-      <c r="E194" s="1" t="s">
-        <v>17</v>
+      <c r="D194" s="5" t="s">
+        <v>4</v>
+      </c>
+      <c r="E194" s="6" t="s">
+        <v>5</v>
       </c>
       <c r="F194" s="2" t="s">
         <v>2</v>
@@ -3310,14 +3313,14 @@
       <c r="H194" s="4"/>
     </row>
     <row r="195" ht="36.0" customHeight="1">
-      <c r="D195" s="6" t="s">
-        <v>20</v>
-      </c>
-      <c r="E195" s="1" t="s">
-        <v>21</v>
+      <c r="D195" s="5" t="s">
+        <v>4</v>
+      </c>
+      <c r="E195" s="6" t="s">
+        <v>5</v>
       </c>
       <c r="F195" s="1" t="s">
-        <v>14</v>
+        <v>11</v>
       </c>
       <c r="G195" s="1" t="s">
         <v>7</v>
@@ -3332,10 +3335,10 @@
         <v>9</v>
       </c>
       <c r="F196" s="3" t="s">
-        <v>18</v>
+        <v>13</v>
       </c>
       <c r="G196" s="3" t="s">
-        <v>19</v>
+        <v>14</v>
       </c>
       <c r="H196" s="4"/>
     </row>
@@ -3347,52 +3350,52 @@
         <v>1</v>
       </c>
       <c r="F197" s="1" t="s">
-        <v>14</v>
-      </c>
-      <c r="G197" s="5" t="s">
-        <v>15</v>
+        <v>11</v>
+      </c>
+      <c r="G197" s="6" t="s">
+        <v>12</v>
       </c>
       <c r="H197" s="4"/>
     </row>
     <row r="198" ht="36.0" customHeight="1">
       <c r="D198" s="1" t="s">
-        <v>4</v>
+        <v>21</v>
       </c>
       <c r="E198" s="1" t="s">
-        <v>5</v>
-      </c>
-      <c r="F198" s="5" t="s">
+        <v>22</v>
+      </c>
+      <c r="F198" s="6" t="s">
+        <v>28</v>
+      </c>
+      <c r="G198" s="1" t="s">
+        <v>10</v>
+      </c>
+      <c r="H198" s="4"/>
+    </row>
+    <row r="199" ht="36.0" customHeight="1">
+      <c r="D199" s="5" t="s">
+        <v>4</v>
+      </c>
+      <c r="E199" s="6" t="s">
+        <v>5</v>
+      </c>
+      <c r="F199" s="2" t="s">
+        <v>2</v>
+      </c>
+      <c r="G199" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="H199" s="4"/>
+    </row>
+    <row r="200" ht="36.0" customHeight="1">
+      <c r="D200" s="7" t="s">
+        <v>23</v>
+      </c>
+      <c r="E200" s="1" t="s">
         <v>24</v>
       </c>
-      <c r="G198" s="1" t="s">
-        <v>11</v>
-      </c>
-      <c r="H198" s="4"/>
-    </row>
-    <row r="199" ht="36.0" customHeight="1">
-      <c r="D199" s="1" t="s">
-        <v>8</v>
-      </c>
-      <c r="E199" s="1" t="s">
-        <v>9</v>
-      </c>
-      <c r="F199" s="2" t="s">
-        <v>2</v>
-      </c>
-      <c r="G199" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="H199" s="4"/>
-    </row>
-    <row r="200" ht="36.0" customHeight="1">
-      <c r="D200" s="6" t="s">
-        <v>12</v>
-      </c>
-      <c r="E200" s="1" t="s">
-        <v>13</v>
-      </c>
       <c r="F200" s="2" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="G200" s="1" t="s">
         <v>7</v>
@@ -3400,75 +3403,75 @@
       <c r="H200" s="4"/>
     </row>
     <row r="201" ht="36.0" customHeight="1">
-      <c r="D201" s="6" t="s">
-        <v>16</v>
-      </c>
-      <c r="E201" s="1" t="s">
-        <v>17</v>
-      </c>
-      <c r="F201" s="5" t="s">
-        <v>22</v>
+      <c r="D201" s="5" t="s">
+        <v>4</v>
+      </c>
+      <c r="E201" s="6" t="s">
+        <v>5</v>
+      </c>
+      <c r="F201" s="6" t="s">
+        <v>17</v>
       </c>
       <c r="G201" s="1" t="s">
-        <v>23</v>
+        <v>18</v>
       </c>
       <c r="H201" s="4"/>
     </row>
     <row r="202" ht="36.0" customHeight="1">
-      <c r="D202" s="6"/>
-      <c r="E202" s="7"/>
+      <c r="D202" s="7"/>
+      <c r="E202" s="8"/>
       <c r="F202" s="2"/>
-      <c r="G202" s="7"/>
-      <c r="H202" s="7"/>
+      <c r="G202" s="8"/>
+      <c r="H202" s="8"/>
     </row>
     <row r="203" ht="36.0" customHeight="1">
-      <c r="D203" s="6"/>
-      <c r="E203" s="7"/>
+      <c r="D203" s="7"/>
+      <c r="E203" s="8"/>
       <c r="F203" s="2"/>
-      <c r="G203" s="7"/>
-      <c r="H203" s="7"/>
+      <c r="G203" s="8"/>
+      <c r="H203" s="8"/>
     </row>
     <row r="204" ht="36.0" customHeight="1">
-      <c r="D204" s="6"/>
-      <c r="E204" s="7"/>
+      <c r="D204" s="7"/>
+      <c r="E204" s="8"/>
       <c r="F204" s="2"/>
-      <c r="G204" s="7"/>
-      <c r="H204" s="7"/>
+      <c r="G204" s="8"/>
+      <c r="H204" s="8"/>
     </row>
     <row r="205" ht="36.0" customHeight="1">
-      <c r="D205" s="6"/>
-      <c r="E205" s="7"/>
+      <c r="D205" s="7"/>
+      <c r="E205" s="8"/>
       <c r="F205" s="2"/>
-      <c r="G205" s="7"/>
-      <c r="H205" s="7"/>
+      <c r="G205" s="8"/>
+      <c r="H205" s="8"/>
     </row>
     <row r="206" ht="36.0" customHeight="1">
-      <c r="D206" s="6"/>
-      <c r="E206" s="7"/>
+      <c r="D206" s="7"/>
+      <c r="E206" s="8"/>
       <c r="F206" s="2"/>
-      <c r="G206" s="7"/>
-      <c r="H206" s="7"/>
+      <c r="G206" s="8"/>
+      <c r="H206" s="8"/>
     </row>
     <row r="207" ht="36.0" customHeight="1">
-      <c r="D207" s="6"/>
-      <c r="E207" s="7"/>
+      <c r="D207" s="7"/>
+      <c r="E207" s="8"/>
       <c r="F207" s="2"/>
-      <c r="G207" s="7"/>
-      <c r="H207" s="7"/>
+      <c r="G207" s="8"/>
+      <c r="H207" s="8"/>
     </row>
     <row r="208" ht="36.0" customHeight="1">
-      <c r="D208" s="6"/>
-      <c r="E208" s="7"/>
+      <c r="D208" s="7"/>
+      <c r="E208" s="8"/>
       <c r="F208" s="2"/>
-      <c r="G208" s="7"/>
-      <c r="H208" s="7"/>
+      <c r="G208" s="8"/>
+      <c r="H208" s="8"/>
     </row>
     <row r="209" ht="36.0" customHeight="1">
-      <c r="D209" s="6"/>
-      <c r="E209" s="7"/>
+      <c r="D209" s="7"/>
+      <c r="E209" s="8"/>
       <c r="F209" s="2"/>
-      <c r="G209" s="7"/>
-      <c r="H209" s="7"/>
+      <c r="G209" s="8"/>
+      <c r="H209" s="8"/>
     </row>
   </sheetData>
   <drawing r:id="rId1"/>

--- a/playlists_02_A.xlsx
+++ b/playlists_02_A.xlsx
@@ -25,10 +25,10 @@
     <t>33uRcSdNVZijCXq6qQnpuU</t>
   </si>
   <si>
-    <t>acraze</t>
+    <t>anyma</t>
   </si>
   <si>
-    <t>4pnp4w9g30yLfVIAFnZMRd</t>
+    <t>4iBwchw0U0GZv5RfVYSMxN</t>
   </si>
   <si>
     <t>eletronicas 2026 mais tocadas</t>
